--- a/deliverables/qc_register/PP_Batch_QC_Testing_Results_Register.xlsx
+++ b/deliverables/qc_register/PP_Batch_QC_Testing_Results_Register.xlsx
@@ -4750,8 +4750,8 @@
       <c r="L33" s="10" t="n">
         <v>23.7</v>
       </c>
-      <c r="M33" s="10" t="n">
-        <v>26.2</v>
+      <c r="M33" s="14" t="n">
+        <v>0.09</v>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
@@ -22772,8 +22772,8 @@
         <is>
           <t>627-1128-25 · 02.07.2025 · IJZ-MB
 197-11-K-26 · 07.08.2026 · FHM
+QCCoA 001 · 10.07.2025 · PP
 ППК25174 · 10.07.2025 · CNP
-QCCoA 001 · 10.07.2025 · PP
 197-11-M-26 · 10.08.2026 · FHM
 QCCoA 001 · 17.07.2025 · PP
 3176-2025 · 26.06.2025 · IJZ</t>
@@ -22975,8 +22975,8 @@
       <c r="F19" s="22" t="inlineStr">
         <is>
           <t>QCCoA 001v02 · 21.01.2026 · PP
+3638-2025 · 28.07.2025 · IJZ
 ППК25211 · 28.07.2025 · CNP
-3638-2025 · 28.07.2025 · IJZ
 767-1376-25 · 29.07.2025 · IJZ-MB</t>
         </is>
       </c>
@@ -23620,8 +23620,8 @@
       <c r="F36" s="22" t="inlineStr">
         <is>
           <t>1226-2192-25 · 05.12.2025 · IJZ-MB
+ППК25380 · 12.12.2025 · CNP
 5888-2025 · 12.12.2025 · IJZ
-ППК25380 · 12.12.2025 · CNP
 QCCoA 001v02 · 21.01.2026 · PP</t>
         </is>
       </c>
@@ -24107,8 +24107,8 @@
       </c>
       <c r="F49" s="22" t="inlineStr">
         <is>
-          <t>100-1-K-26 · 09.04.2026 · FHM
-100-1-LoD-26 · 09.04.2026 · FHM</t>
+          <t>100-1-LoD-26 · 09.04.2026 · FHM
+100-1-K-26 · 09.04.2026 · FHM</t>
         </is>
       </c>
       <c r="G49" s="22" t="inlineStr">
@@ -26274,7 +26274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -26896,90 +26896,112 @@
     <row r="34">
       <c r="A34" s="28" t="inlineStr">
         <is>
+          <t>CJ072501</t>
+        </is>
+      </c>
+      <c r="B34" s="28" t="inlineStr">
+        <is>
+          <t>Total CBD</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>extraction row misassignment (took Δ9-THCA 26.20); 0.09 confirmed on paper original by QC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
           <t>AB092501</t>
         </is>
       </c>
-      <c r="B34" s="28" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>Total Δ9-THC</t>
         </is>
       </c>
-      <c r="C34" s="29" t="inlineStr">
+      <c r="C35" s="29" t="inlineStr">
         <is>
           <t>16.93</t>
         </is>
       </c>
-      <c r="D34" s="30" t="inlineStr">
+      <c r="D35" s="30" t="inlineStr">
         <is>
           <t>extraction line-pick error, corrected from certificate text</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>D — Batches in the database but NOT in the prior Batch-Release register</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="31" t="inlineStr">
-        <is>
-          <t>GG1024</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="31" t="inlineStr">
         <is>
-          <t>OMP1024_01</t>
+          <t>GG1024</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="31" t="inlineStr">
         <is>
-          <t>BSS1024_01/1</t>
+          <t>OMP1024_01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="31" t="inlineStr">
         <is>
-          <t>CJ052501/01</t>
+          <t>BSS1024_01/1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="31" t="inlineStr">
         <is>
-          <t>CJ052501/02</t>
+          <t>CJ052501/01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="31" t="inlineStr">
         <is>
-          <t>FB012601_1</t>
+          <t>CJ052501/02</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="31" t="inlineStr">
         <is>
-          <t>GG012601*</t>
+          <t>FB012601_1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="31" t="inlineStr">
         <is>
-          <t>JD012601*</t>
+          <t>GG012601*</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>JD012601*</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="inlineStr">
         <is>
           <t>JD112501*</t>
         </is>

--- a/deliverables/qc_register/PP_Batch_QC_Testing_Results_Register.xlsx
+++ b/deliverables/qc_register/PP_Batch_QC_Testing_Results_Register.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF83"/>
+  <dimension ref="A1:AF84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AF6" s="6" t="inlineStr">
         <is>
-          <t>Не одговара</t>
+          <t>н.д.</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AF14" s="6" t="inlineStr">
         <is>
-          <t>Не одговара</t>
+          <t>Н.Д.</t>
         </is>
       </c>
     </row>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="W27" s="6" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Одговара</t>
         </is>
       </c>
       <c r="X27" s="6" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Одговара</t>
         </is>
       </c>
       <c r="Y27" s="6" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="AF32" s="6" t="inlineStr">
         <is>
-          <t>N.D.</t>
+          <t>≤ LOQ</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="AF33" s="6" t="inlineStr">
         <is>
-          <t>Не одговара</t>
+          <t>Н.д.</t>
         </is>
       </c>
     </row>
@@ -6354,12 +6354,12 @@
       </c>
       <c r="W44" s="6" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Одговара</t>
         </is>
       </c>
       <c r="X44" s="6" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Одговара</t>
         </is>
       </c>
       <c r="Y44" s="6" t="inlineStr">
@@ -8332,46 +8332,40 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="C58" s="6" t="n">
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>J31122501 (hand-trimmed)</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>P060262</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>J31_THC21.5:CBD1</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="n"/>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>J31122501</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>P060262</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>Jokerz 31</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>J31_THC20:CBD1</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>CoQ-PP-2026-0054</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>07.04.2026</t>
-        </is>
-      </c>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>23.04.2026</t>
-        </is>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>6</v>
       </c>
       <c r="L58" s="10" t="n">
         <v>19.84</v>
@@ -8412,10 +8406,10 @@
         </is>
       </c>
       <c r="T58" s="15" t="n">
-        <v>1900</v>
+        <v>850</v>
       </c>
       <c r="U58" s="15" t="n">
-        <v>840</v>
+        <v>370</v>
       </c>
       <c r="V58" s="11" t="inlineStr">
         <is>
@@ -8424,52 +8418,50 @@
       </c>
       <c r="W58" s="6" t="inlineStr">
         <is>
-          <t>Одговара</t>
+          <t>Отсутна</t>
         </is>
       </c>
       <c r="X58" s="6" t="inlineStr">
         <is>
-          <t>Одговара</t>
-        </is>
-      </c>
-      <c r="Y58" s="6" t="inlineStr">
-        <is>
-          <t>N.D.</t>
-        </is>
+          <t>Отсуствa</t>
+        </is>
+      </c>
+      <c r="Y58" s="16" t="n">
+        <v>2.5</v>
       </c>
       <c r="Z58" s="6" t="inlineStr">
         <is>
-          <t>N.D.</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="AA58" s="6" t="inlineStr">
         <is>
-          <t>N.D.</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="AB58" s="6" t="inlineStr">
         <is>
-          <t>N.D.</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="AC58" s="6" t="inlineStr">
         <is>
-          <t>N.D.</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="AD58" s="6" t="inlineStr">
         <is>
-          <t>N.D.</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="AE58" s="6" t="inlineStr">
         <is>
-          <t>N.D.</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="AF58" s="6" t="inlineStr">
         <is>
-          <t>Н.д.</t>
+          <t>н.д.</t>
         </is>
       </c>
     </row>
@@ -8482,32 +8474,30 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="C59" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="C59" s="6" t="n"/>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>OPM122501</t>
+          <t>J31122501 (machine-trimmed)</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>P060242</t>
+          <t>P060262</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>OPM_THC10:CBD1</t>
+          <t>J31_THC21.5:CBD1</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0055</t>
+          <t>CoQ-PP-2026-0054</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
@@ -8517,27 +8507,29 @@
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="K59" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L59" s="8" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="M59" s="9" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L59" s="10" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="M59" s="6" t="inlineStr">
         <is>
           <t>&lt;LOQ</t>
         </is>
       </c>
-      <c r="N59" s="9" t="inlineStr">
+      <c r="N59" s="6" t="inlineStr">
         <is>
           <t>&lt;LOQ</t>
         </is>
       </c>
-      <c r="O59" s="16" t="n">
-        <v>6.6</v>
+      <c r="O59" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P59" s="11" t="inlineStr">
         <is>
@@ -8560,14 +8552,14 @@
         </is>
       </c>
       <c r="T59" s="15" t="n">
-        <v>120</v>
+        <v>1900</v>
       </c>
       <c r="U59" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="V59" s="6" t="inlineStr">
-        <is>
-          <t>&lt; 10</t>
+        <v>840</v>
+      </c>
+      <c r="V59" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="W59" s="6" t="inlineStr">
@@ -8580,38 +8572,44 @@
           <t>Одговара</t>
         </is>
       </c>
-      <c r="Y59" s="16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z59" s="9" t="inlineStr">
-        <is>
-          <t>ND</t>
+      <c r="Y59" s="6" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="Z59" s="6" t="inlineStr">
+        <is>
+          <t>N.D.</t>
         </is>
       </c>
       <c r="AA59" s="6" t="inlineStr">
         <is>
-          <t>Н.Д.</t>
-        </is>
-      </c>
-      <c r="AB59" s="12" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="AC59" s="12" t="n">
-        <v>0.165</v>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="AB59" s="6" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
+      </c>
+      <c r="AC59" s="6" t="inlineStr">
+        <is>
+          <t>N.D.</t>
+        </is>
       </c>
       <c r="AD59" s="6" t="inlineStr">
         <is>
-          <t>Н.Д.</t>
+          <t>N.D.</t>
         </is>
       </c>
       <c r="AE59" s="6" t="inlineStr">
         <is>
-          <t>Н.Д.</t>
+          <t>N.D.</t>
         </is>
       </c>
       <c r="AF59" s="6" t="inlineStr">
         <is>
-          <t>Н.Д.</t>
+          <t>Н.д.</t>
         </is>
       </c>
     </row>
@@ -8621,63 +8619,65 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>CC112501</t>
+          <t>OPM122501</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>P060272</t>
+          <t>P060242</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>CC_THC13:CBD1</t>
+          <t>OPM_THC10:CBD1</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0056</t>
+          <t>CoQ-PP-2026-0055</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>28.04.2026</t>
+          <t>07.04.2026</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="K60" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L60" s="10" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="M60" s="10" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="N60" s="6" t="inlineStr">
-        <is>
-          <t>BLQ</t>
-        </is>
-      </c>
-      <c r="O60" s="10" t="n">
-        <v>7.39</v>
+        <v>6</v>
+      </c>
+      <c r="L60" s="8" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>&lt;LOQ</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr">
+        <is>
+          <t>&lt;LOQ</t>
+        </is>
+      </c>
+      <c r="O60" s="16" t="n">
+        <v>6.6</v>
       </c>
       <c r="P60" s="11" t="inlineStr">
         <is>
@@ -8699,61 +8699,59 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T60" s="6" t="inlineStr">
-        <is>
-          <t>3,8 x 10^3</t>
-        </is>
-      </c>
-      <c r="U60" s="6" t="inlineStr">
-        <is>
-          <t>2,7 x 10^3</t>
-        </is>
+      <c r="T60" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="U60" s="15" t="n">
+        <v>100</v>
       </c>
       <c r="V60" s="6" t="inlineStr">
         <is>
-          <t>&lt;10^3 и &gt;10^2</t>
+          <t>&lt; 10</t>
         </is>
       </c>
       <c r="W60" s="6" t="inlineStr">
         <is>
-          <t>отсутна/25</t>
+          <t>Одговара</t>
         </is>
       </c>
       <c r="X60" s="6" t="inlineStr">
         <is>
-          <t>отсутна/g</t>
-        </is>
-      </c>
-      <c r="Y60" s="6" t="inlineStr">
-        <is>
-          <t>&lt; 2</t>
-        </is>
-      </c>
-      <c r="Z60" s="6" t="inlineStr">
-        <is>
-          <t>N.D.</t>
+          <t>Одговара</t>
+        </is>
+      </c>
+      <c r="Y60" s="16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z60" s="9" t="inlineStr">
+        <is>
+          <t>ND</t>
         </is>
       </c>
       <c r="AA60" s="6" t="inlineStr">
         <is>
-          <t>N.D.</t>
-        </is>
-      </c>
-      <c r="AB60" s="13" t="n">
-        <v>0.0289</v>
-      </c>
-      <c r="AC60" s="13" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="AD60" s="12" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="AE60" s="13" t="n">
-        <v>0.0102</v>
+          <t>Н.Д.</t>
+        </is>
+      </c>
+      <c r="AB60" s="12" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AC60" s="12" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AD60" s="6" t="inlineStr">
+        <is>
+          <t>Н.Д.</t>
+        </is>
+      </c>
+      <c r="AE60" s="6" t="inlineStr">
+        <is>
+          <t>Н.Д.</t>
+        </is>
       </c>
       <c r="AF60" s="6" t="inlineStr">
         <is>
-          <t>N.D.</t>
+          <t>Н.Д.</t>
         </is>
       </c>
     </row>
@@ -8763,35 +8761,35 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>FB012601_1</t>
+          <t>CC112501</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>P060322</t>
+          <t>P060272</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>FB_THC16.5:CBD1</t>
+          <t>CC_THC13:CBD1</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0061</t>
+          <t>CoQ-PP-2026-0056</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
@@ -8808,20 +8806,18 @@
         <v>3</v>
       </c>
       <c r="L61" s="10" t="n">
-        <v>14.68</v>
-      </c>
-      <c r="M61" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N61" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>13.35</v>
+      </c>
+      <c r="M61" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>BLQ</t>
         </is>
       </c>
       <c r="O61" s="10" t="n">
-        <v>7.67</v>
+        <v>7.39</v>
       </c>
       <c r="P61" s="11" t="inlineStr">
         <is>
@@ -8845,17 +8841,17 @@
       </c>
       <c r="T61" s="6" t="inlineStr">
         <is>
-          <t>2 x 10³</t>
+          <t>3,8 x 10^3</t>
         </is>
       </c>
       <c r="U61" s="6" t="inlineStr">
         <is>
-          <t>2,1 x 10³</t>
+          <t>2,7 x 10^3</t>
         </is>
       </c>
       <c r="V61" s="6" t="inlineStr">
         <is>
-          <t>&lt; 10</t>
+          <t>&lt;10^3 и &gt;10^2</t>
         </is>
       </c>
       <c r="W61" s="6" t="inlineStr">
@@ -8884,20 +8880,20 @@
         </is>
       </c>
       <c r="AB61" s="13" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="AC61" s="12" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="AD61" s="13" t="n">
-        <v>0.0144</v>
+        <v>0.0289</v>
+      </c>
+      <c r="AC61" s="13" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="AD61" s="12" t="n">
+        <v>0.016</v>
       </c>
       <c r="AE61" s="13" t="n">
-        <v>0.0155</v>
+        <v>0.0102</v>
       </c>
       <c r="AF61" s="6" t="inlineStr">
         <is>
-          <t>Не одговара</t>
+          <t>N.D.</t>
         </is>
       </c>
     </row>
@@ -8907,20 +8903,20 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>FB012601_1</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>P060292</t>
+          <t>P060322</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -8935,7 +8931,7 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0057</t>
+          <t>CoQ-PP-2026-0061</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
@@ -8952,7 +8948,7 @@
         <v>3</v>
       </c>
       <c r="L62" s="10" t="n">
-        <v>16.69</v>
+        <v>14.68</v>
       </c>
       <c r="M62" s="11" t="inlineStr">
         <is>
@@ -8965,7 +8961,7 @@
         </is>
       </c>
       <c r="O62" s="10" t="n">
-        <v>6.09</v>
+        <v>7.67</v>
       </c>
       <c r="P62" s="11" t="inlineStr">
         <is>
@@ -8989,22 +8985,22 @@
       </c>
       <c r="T62" s="6" t="inlineStr">
         <is>
-          <t>3,9 x 10³ CFU/g</t>
+          <t>2 x 10³</t>
         </is>
       </c>
       <c r="U62" s="6" t="inlineStr">
         <is>
-          <t>2,4 x 10³ CFU/g</t>
+          <t>2,1 x 10³</t>
         </is>
       </c>
       <c r="V62" s="6" t="inlineStr">
         <is>
-          <t>&lt; 10 CFU/g</t>
+          <t>&lt; 10</t>
         </is>
       </c>
       <c r="W62" s="6" t="inlineStr">
         <is>
-          <t>отсутна/25 g</t>
+          <t>отсутна/25</t>
         </is>
       </c>
       <c r="X62" s="6" t="inlineStr">
@@ -9019,25 +9015,25 @@
       </c>
       <c r="Z62" s="6" t="inlineStr">
         <is>
-          <t>Н.Д.</t>
+          <t>N.D.</t>
         </is>
       </c>
       <c r="AA62" s="6" t="inlineStr">
         <is>
-          <t>Н.Д.</t>
+          <t>N.D.</t>
         </is>
       </c>
       <c r="AB62" s="13" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="AC62" s="13" t="n">
-        <v>0.0108</v>
+        <v>0.0114</v>
+      </c>
+      <c r="AC62" s="12" t="n">
+        <v>0.017</v>
       </c>
       <c r="AD62" s="13" t="n">
-        <v>0.0199</v>
+        <v>0.0144</v>
       </c>
       <c r="AE62" s="13" t="n">
-        <v>0.0078</v>
+        <v>0.0155</v>
       </c>
       <c r="AF62" s="6" t="inlineStr">
         <is>
@@ -9049,17 +9045,39 @@
       <c r="A63" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="6" t="n"/>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>GG012601*</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="6" t="n"/>
-      <c r="G63" s="6" t="n"/>
-      <c r="H63" s="6" t="n"/>
+          <t>FB112501</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>P060292</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>FB_THC16.5:CBD1</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0057</t>
+        </is>
+      </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
           <t>28.04.2026</t>
@@ -9074,7 +9092,7 @@
         <v>3</v>
       </c>
       <c r="L63" s="10" t="n">
-        <v>15.35</v>
+        <v>16.69</v>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
@@ -9087,7 +9105,7 @@
         </is>
       </c>
       <c r="O63" s="10" t="n">
-        <v>6.13</v>
+        <v>6.09</v>
       </c>
       <c r="P63" s="11" t="inlineStr">
         <is>
@@ -9111,12 +9129,12 @@
       </c>
       <c r="T63" s="6" t="inlineStr">
         <is>
-          <t>1 x 10⁴ CFU/g</t>
+          <t>3,9 x 10³ CFU/g</t>
         </is>
       </c>
       <c r="U63" s="6" t="inlineStr">
         <is>
-          <t>1 x 10⁴ CFU/g</t>
+          <t>2,4 x 10³ CFU/g</t>
         </is>
       </c>
       <c r="V63" s="6" t="inlineStr">
@@ -9150,16 +9168,16 @@
         </is>
       </c>
       <c r="AB63" s="13" t="n">
-        <v>0.0227</v>
+        <v>0.0215</v>
       </c>
       <c r="AC63" s="13" t="n">
-        <v>0.0179</v>
+        <v>0.0108</v>
       </c>
       <c r="AD63" s="13" t="n">
-        <v>0.0163</v>
-      </c>
-      <c r="AE63" s="12" t="n">
-        <v>0.031</v>
+        <v>0.0199</v>
+      </c>
+      <c r="AE63" s="13" t="n">
+        <v>0.0078</v>
       </c>
       <c r="AF63" s="6" t="inlineStr">
         <is>
@@ -9171,39 +9189,17 @@
       <c r="A64" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="n">
-        <v>3</v>
-      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>GG112501</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>P060252</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>Gorilla Glue</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>GG_THC15:CBD1</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>CoQ-PP-2026-0058</t>
-        </is>
-      </c>
+          <t>GG012601*</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n"/>
+      <c r="G64" s="6" t="n"/>
+      <c r="H64" s="6" t="n"/>
       <c r="I64" s="6" t="inlineStr">
         <is>
           <t>28.04.2026</t>
@@ -9218,10 +9214,12 @@
         <v>3</v>
       </c>
       <c r="L64" s="10" t="n">
-        <v>17.94</v>
-      </c>
-      <c r="M64" s="10" t="n">
-        <v>0.08</v>
+        <v>15.35</v>
+      </c>
+      <c r="M64" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N64" s="11" t="inlineStr">
         <is>
@@ -9229,7 +9227,7 @@
         </is>
       </c>
       <c r="O64" s="10" t="n">
-        <v>6.31</v>
+        <v>6.13</v>
       </c>
       <c r="P64" s="11" t="inlineStr">
         <is>
@@ -9253,27 +9251,27 @@
       </c>
       <c r="T64" s="6" t="inlineStr">
         <is>
-          <t>5,1 x 10^3</t>
+          <t>1 x 10⁴ CFU/g</t>
         </is>
       </c>
       <c r="U64" s="6" t="inlineStr">
         <is>
-          <t>4,5 x 10^3</t>
-        </is>
-      </c>
-      <c r="V64" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>1 x 10⁴ CFU/g</t>
+        </is>
+      </c>
+      <c r="V64" s="6" t="inlineStr">
+        <is>
+          <t>&lt; 10 CFU/g</t>
         </is>
       </c>
       <c r="W64" s="6" t="inlineStr">
         <is>
-          <t>отсутна/25 г</t>
+          <t>отсутна/25 g</t>
         </is>
       </c>
       <c r="X64" s="6" t="inlineStr">
         <is>
-          <t>отсутен/г</t>
+          <t>отсутна/g</t>
         </is>
       </c>
       <c r="Y64" s="6" t="inlineStr">
@@ -9291,21 +9289,21 @@
           <t>Н.Д.</t>
         </is>
       </c>
-      <c r="AB64" s="12" t="n">
-        <v>0.033</v>
+      <c r="AB64" s="13" t="n">
+        <v>0.0227</v>
       </c>
       <c r="AC64" s="13" t="n">
-        <v>0.0154</v>
+        <v>0.0179</v>
       </c>
       <c r="AD64" s="13" t="n">
-        <v>0.0272</v>
-      </c>
-      <c r="AE64" s="13" t="n">
-        <v>0.0146</v>
+        <v>0.0163</v>
+      </c>
+      <c r="AE64" s="12" t="n">
+        <v>0.031</v>
       </c>
       <c r="AF64" s="6" t="inlineStr">
         <is>
-          <t>Н.Д.</t>
+          <t>Н.д.</t>
         </is>
       </c>
     </row>
@@ -9313,17 +9311,39 @@
       <c r="A65" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="B65" s="6" t="n"/>
-      <c r="C65" s="6" t="n"/>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>JD012601*</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="6" t="n"/>
-      <c r="G65" s="6" t="n"/>
-      <c r="H65" s="6" t="n"/>
+          <t>GG112501</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>P060252</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>GG_THC15:CBD1</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0058</t>
+        </is>
+      </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
           <t>28.04.2026</t>
@@ -9338,18 +9358,18 @@
         <v>3</v>
       </c>
       <c r="L65" s="10" t="n">
-        <v>18.16</v>
+        <v>17.94</v>
       </c>
       <c r="M65" s="10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N65" s="6" t="inlineStr">
-        <is>
-          <t>BLQ</t>
+        <v>0.08</v>
+      </c>
+      <c r="N65" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="O65" s="10" t="n">
-        <v>6.68</v>
+        <v>6.31</v>
       </c>
       <c r="P65" s="11" t="inlineStr">
         <is>
@@ -9373,12 +9393,12 @@
       </c>
       <c r="T65" s="6" t="inlineStr">
         <is>
-          <t>1,9 x 10³ CFU/g</t>
+          <t>5,1 x 10^3</t>
         </is>
       </c>
       <c r="U65" s="6" t="inlineStr">
         <is>
-          <t>2,4 x 10² CFU/g</t>
+          <t>4,5 x 10^3</t>
         </is>
       </c>
       <c r="V65" s="11" t="inlineStr">
@@ -9388,12 +9408,12 @@
       </c>
       <c r="W65" s="6" t="inlineStr">
         <is>
-          <t>отсутна/25 g</t>
+          <t>отсутна/25 г</t>
         </is>
       </c>
       <c r="X65" s="6" t="inlineStr">
         <is>
-          <t>отсутна/g</t>
+          <t>отсутен/г</t>
         </is>
       </c>
       <c r="Y65" s="6" t="inlineStr">
@@ -9411,21 +9431,21 @@
           <t>Н.Д.</t>
         </is>
       </c>
-      <c r="AB65" s="13" t="n">
-        <v>0.07389999999999999</v>
+      <c r="AB65" s="12" t="n">
+        <v>0.033</v>
       </c>
       <c r="AC65" s="13" t="n">
-        <v>0.0166</v>
+        <v>0.0154</v>
       </c>
       <c r="AD65" s="13" t="n">
-        <v>0.0136</v>
+        <v>0.0272</v>
       </c>
       <c r="AE65" s="13" t="n">
-        <v>0.0322</v>
+        <v>0.0146</v>
       </c>
       <c r="AF65" s="6" t="inlineStr">
         <is>
-          <t>Н.д.</t>
+          <t>Н.Д.</t>
         </is>
       </c>
     </row>
@@ -9434,25 +9454,15 @@
         <v>61</v>
       </c>
       <c r="B66" s="6" t="n"/>
-      <c r="C66" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="C66" s="6" t="n"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>JD112501</t>
+          <t>JD012601*</t>
         </is>
       </c>
       <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>Jelly Donutz</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>CAYN JD 20/1</t>
-        </is>
-      </c>
+      <c r="F66" s="6" t="n"/>
+      <c r="G66" s="6" t="n"/>
       <c r="H66" s="6" t="n"/>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -9461,27 +9471,25 @@
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="K66" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="L66" s="8" t="n">
-        <v>20.32</v>
-      </c>
-      <c r="M66" s="6" t="inlineStr">
-        <is>
-          <t>&lt; LOQ</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="L66" s="10" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="M66" s="10" t="n">
+        <v>0.06</v>
       </c>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>&lt; LOQ</t>
+          <t>BLQ</t>
         </is>
       </c>
       <c r="O66" s="10" t="n">
-        <v>6.69</v>
+        <v>6.68</v>
       </c>
       <c r="P66" s="11" t="inlineStr">
         <is>
@@ -9505,12 +9513,12 @@
       </c>
       <c r="T66" s="6" t="inlineStr">
         <is>
-          <t>2,6 x 10^3</t>
+          <t>1,9 x 10³ CFU/g</t>
         </is>
       </c>
       <c r="U66" s="6" t="inlineStr">
         <is>
-          <t>3,3 x 10^3</t>
+          <t>2,4 x 10² CFU/g</t>
         </is>
       </c>
       <c r="V66" s="11" t="inlineStr">
@@ -9520,7 +9528,7 @@
       </c>
       <c r="W66" s="6" t="inlineStr">
         <is>
-          <t>отсутна/25</t>
+          <t>отсутна/25 g</t>
         </is>
       </c>
       <c r="X66" s="6" t="inlineStr">
@@ -9533,9 +9541,9 @@
           <t>&lt; 2</t>
         </is>
       </c>
-      <c r="Z66" s="9" t="inlineStr">
-        <is>
-          <t>ND</t>
+      <c r="Z66" s="6" t="inlineStr">
+        <is>
+          <t>Н.Д.</t>
         </is>
       </c>
       <c r="AA66" s="6" t="inlineStr">
@@ -9543,21 +9551,21 @@
           <t>Н.Д.</t>
         </is>
       </c>
-      <c r="AB66" s="12" t="n">
-        <v>0.022</v>
+      <c r="AB66" s="13" t="n">
+        <v>0.07389999999999999</v>
       </c>
       <c r="AC66" s="13" t="n">
-        <v>0.0149</v>
-      </c>
-      <c r="AD66" s="10" t="n">
-        <v>0.02</v>
+        <v>0.0166</v>
+      </c>
+      <c r="AD66" s="13" t="n">
+        <v>0.0136</v>
       </c>
       <c r="AE66" s="13" t="n">
-        <v>0.0166</v>
+        <v>0.0322</v>
       </c>
       <c r="AF66" s="6" t="inlineStr">
         <is>
-          <t>Н.Д.</t>
+          <t>Н.д.</t>
         </is>
       </c>
     </row>
@@ -9566,15 +9574,25 @@
         <v>62</v>
       </c>
       <c r="B67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
+      <c r="C67" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>JD112501*</t>
+          <t>JD112501</t>
         </is>
       </c>
       <c r="E67" s="6" t="n"/>
-      <c r="F67" s="6" t="n"/>
-      <c r="G67" s="6" t="n"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CAYN JD 20/1</t>
+        </is>
+      </c>
       <c r="H67" s="6" t="n"/>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -9583,27 +9601,27 @@
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="K67" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L67" s="10" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="M67" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5</v>
+      </c>
+      <c r="L67" s="8" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>&lt; LOQ</t>
+        </is>
+      </c>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>&lt; LOQ</t>
         </is>
       </c>
       <c r="O67" s="10" t="n">
-        <v>6.38</v>
+        <v>6.69</v>
       </c>
       <c r="P67" s="11" t="inlineStr">
         <is>
@@ -9627,12 +9645,12 @@
       </c>
       <c r="T67" s="6" t="inlineStr">
         <is>
-          <t>1 x 10⁴ CFU/g</t>
+          <t>2,6 x 10^3</t>
         </is>
       </c>
       <c r="U67" s="6" t="inlineStr">
         <is>
-          <t>6,7 x 10³ CFU/g</t>
+          <t>3,3 x 10^3</t>
         </is>
       </c>
       <c r="V67" s="11" t="inlineStr">
@@ -9642,7 +9660,7 @@
       </c>
       <c r="W67" s="6" t="inlineStr">
         <is>
-          <t>отсутна/25 g</t>
+          <t>отсутна/25</t>
         </is>
       </c>
       <c r="X67" s="6" t="inlineStr">
@@ -9655,31 +9673,31 @@
           <t>&lt; 2</t>
         </is>
       </c>
-      <c r="Z67" s="6" t="inlineStr">
-        <is>
-          <t>N.D.</t>
+      <c r="Z67" s="9" t="inlineStr">
+        <is>
+          <t>ND</t>
         </is>
       </c>
       <c r="AA67" s="6" t="inlineStr">
         <is>
-          <t>N.D.</t>
-        </is>
-      </c>
-      <c r="AB67" s="13" t="n">
-        <v>0.0109</v>
-      </c>
-      <c r="AC67" s="17" t="n">
-        <v>0.01287</v>
-      </c>
-      <c r="AD67" s="13" t="n">
-        <v>0.0175</v>
+          <t>Н.Д.</t>
+        </is>
+      </c>
+      <c r="AB67" s="12" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="AC67" s="13" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="AD67" s="10" t="n">
+        <v>0.02</v>
       </c>
       <c r="AE67" s="13" t="n">
-        <v>0.0165</v>
+        <v>0.0166</v>
       </c>
       <c r="AF67" s="6" t="inlineStr">
         <is>
-          <t>Н.д.</t>
+          <t>Н.Д.</t>
         </is>
       </c>
     </row>
@@ -9687,39 +9705,17 @@
       <c r="A68" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>SCR112501</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>P060282</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>SCR_THC18.5:CBD1</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>CoQ-PP-2026-0060</t>
-        </is>
-      </c>
+          <t>JD112501*</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="n"/>
+      <c r="G68" s="6" t="n"/>
+      <c r="H68" s="6" t="n"/>
       <c r="I68" s="6" t="inlineStr">
         <is>
           <t>28.04.2026</t>
@@ -9734,7 +9730,7 @@
         <v>3</v>
       </c>
       <c r="L68" s="10" t="n">
-        <v>17.13</v>
+        <v>13.93</v>
       </c>
       <c r="M68" s="11" t="inlineStr">
         <is>
@@ -9747,7 +9743,7 @@
         </is>
       </c>
       <c r="O68" s="10" t="n">
-        <v>6.84</v>
+        <v>6.38</v>
       </c>
       <c r="P68" s="11" t="inlineStr">
         <is>
@@ -9771,12 +9767,12 @@
       </c>
       <c r="T68" s="6" t="inlineStr">
         <is>
-          <t>2,3 x 10³</t>
+          <t>1 x 10⁴ CFU/g</t>
         </is>
       </c>
       <c r="U68" s="6" t="inlineStr">
         <is>
-          <t>4,3 x 10³</t>
+          <t>6,7 x 10³ CFU/g</t>
         </is>
       </c>
       <c r="V68" s="11" t="inlineStr">
@@ -9801,25 +9797,25 @@
       </c>
       <c r="Z68" s="6" t="inlineStr">
         <is>
-          <t>Н.д.</t>
+          <t>N.D.</t>
         </is>
       </c>
       <c r="AA68" s="6" t="inlineStr">
         <is>
-          <t>Н.д.</t>
+          <t>N.D.</t>
         </is>
       </c>
       <c r="AB68" s="13" t="n">
-        <v>0.0299</v>
-      </c>
-      <c r="AC68" s="13" t="n">
-        <v>0.0136</v>
+        <v>0.0109</v>
+      </c>
+      <c r="AC68" s="17" t="n">
+        <v>0.01287</v>
       </c>
       <c r="AD68" s="13" t="n">
-        <v>0.0154</v>
-      </c>
-      <c r="AE68" s="12" t="n">
-        <v>0.017</v>
+        <v>0.0175</v>
+      </c>
+      <c r="AE68" s="13" t="n">
+        <v>0.0165</v>
       </c>
       <c r="AF68" s="6" t="inlineStr">
         <is>
@@ -9833,71 +9829,79 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>SCR112501</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>P060282</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>SCR_THC18.5:CBD1</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0060</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>FB012603</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>Fat Bastard</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>FB_THC22:CBD1</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>CoQ-PP-2026-0064</t>
-        </is>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>30.06.2026</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>30.06.2026</t>
-        </is>
-      </c>
-      <c r="K69" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="L69" s="10" t="n">
-        <v>20.83</v>
-      </c>
-      <c r="M69" s="10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="N69" s="10" t="n">
-        <v>0.06</v>
+        <v>17.13</v>
+      </c>
+      <c r="M69" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O69" s="10" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="P69" s="6" t="inlineStr">
-        <is>
-          <t>Одговара</t>
-        </is>
-      </c>
-      <c r="Q69" s="6" t="inlineStr">
-        <is>
-          <t>Одговара</t>
-        </is>
-      </c>
-      <c r="R69" s="6" t="inlineStr">
-        <is>
-          <t>Одговара</t>
+        <v>6.84</v>
+      </c>
+      <c r="P69" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q69" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R69" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="S69" s="11" t="inlineStr">
@@ -9905,14 +9909,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="T69" s="6" t="inlineStr">
+        <is>
+          <t>2,3 x 10³</t>
+        </is>
+      </c>
+      <c r="U69" s="6" t="inlineStr">
+        <is>
+          <t>4,3 x 10³</t>
         </is>
       </c>
       <c r="V69" s="11" t="inlineStr">
@@ -9920,54 +9924,46 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="W69" s="6" t="inlineStr">
+        <is>
+          <t>отсутна/25 g</t>
+        </is>
+      </c>
+      <c r="X69" s="6" t="inlineStr">
+        <is>
+          <t>отсутна/g</t>
+        </is>
+      </c>
+      <c r="Y69" s="6" t="inlineStr">
+        <is>
+          <t>&lt; 2</t>
+        </is>
+      </c>
+      <c r="Z69" s="6" t="inlineStr">
+        <is>
+          <t>Н.д.</t>
+        </is>
+      </c>
+      <c r="AA69" s="6" t="inlineStr">
+        <is>
+          <t>Н.д.</t>
+        </is>
+      </c>
+      <c r="AB69" s="13" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="AC69" s="13" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="AD69" s="13" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="AE69" s="12" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AF69" s="6" t="inlineStr">
+        <is>
+          <t>Н.д.</t>
         </is>
       </c>
     </row>
@@ -9985,14 +9981,10 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>FB012603V</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>P060392</t>
-        </is>
-      </c>
+          <t>FB012603</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n"/>
       <c r="F70" s="6" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
@@ -10000,12 +9992,12 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>FB_THC16.5:CBD1</t>
+          <t>FB_THC22:CBD1</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0065</t>
+          <t>CoQ-PP-2026-0064</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
@@ -10022,20 +10014,20 @@
         <v>1</v>
       </c>
       <c r="L70" s="10" t="n">
-        <v>18.29</v>
+        <v>20.83</v>
       </c>
       <c r="M70" s="10" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="N70" s="10" t="n">
         <v>0.06</v>
       </c>
       <c r="O70" s="10" t="n">
-        <v>6.36</v>
+        <v>7.04</v>
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Одговара</t>
         </is>
       </c>
       <c r="Q70" s="6" t="inlineStr">
@@ -10129,64 +10121,62 @@
         </is>
       </c>
       <c r="C71" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>FB012603V</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>P060392</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>FB_THC16.5:CBD1</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0065</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>GG012603</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>P060402</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>Gorilla Glue</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>GG_THC15:CBD1</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>CoQ-PP-2026-0094</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>30.06.2026</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>10.08.2026</t>
-        </is>
-      </c>
-      <c r="K71" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="L71" s="10" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="M71" s="6" t="inlineStr">
-        <is>
-          <t>&lt; LOQ</t>
-        </is>
-      </c>
-      <c r="N71" s="6" t="inlineStr">
-        <is>
-          <t>&lt; LOQ</t>
-        </is>
+        <v>18.29</v>
+      </c>
+      <c r="M71" s="10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N71" s="10" t="n">
+        <v>0.06</v>
       </c>
       <c r="O71" s="10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="P71" s="10" t="n">
-        <v>0.05</v>
+        <v>6.36</v>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>Одговара</t>
+        </is>
       </c>
       <c r="Q71" s="6" t="inlineStr">
         <is>
@@ -10228,19 +10218,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Y71" s="6" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="Z71" s="6" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="AA71" s="6" t="inlineStr">
-        <is>
-          <t>ND</t>
+      <c r="Y71" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z71" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA71" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="AB71" s="11" t="inlineStr">
@@ -10273,27 +10263,39 @@
       <c r="A72" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B72" s="6" t="n"/>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
       <c r="C72" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>JD012603_02</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="n"/>
+          <t>GG012603</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>P060402</t>
+        </is>
+      </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>CAYN JD 20/1</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="n"/>
+          <t>GG_THC15:CBD1</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0094</t>
+        </is>
+      </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
           <t>30.06.2026</t>
@@ -10301,39 +10303,41 @@
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>30.06.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="K72" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L72" s="10" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="M72" s="10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N72" s="10" t="n">
-        <v>0.05</v>
+        <v>16.7</v>
+      </c>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t>&lt; LOQ</t>
+        </is>
+      </c>
+      <c r="N72" s="6" t="inlineStr">
+        <is>
+          <t>&lt; LOQ</t>
+        </is>
       </c>
       <c r="O72" s="10" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="P72" s="6" t="inlineStr">
+        <v>6.48</v>
+      </c>
+      <c r="P72" s="10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
         <is>
           <t>Одговара</t>
         </is>
       </c>
-      <c r="Q72" s="6" t="inlineStr">
+      <c r="R72" s="6" t="inlineStr">
         <is>
           <t>Одговара</t>
         </is>
       </c>
-      <c r="R72" s="6" t="inlineStr">
-        <is>
-          <t>Одговара</t>
-        </is>
-      </c>
       <c r="S72" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -10364,19 +10368,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Y72" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z72" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA72" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Y72" s="6" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="Z72" s="6" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="AA72" s="6" t="inlineStr">
+        <is>
+          <t>ND</t>
         </is>
       </c>
       <c r="AB72" s="11" t="inlineStr">
@@ -10415,7 +10419,7 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>JD012603_02V</t>
+          <t>JD012603_02</t>
         </is>
       </c>
       <c r="E73" s="6" t="n"/>
@@ -10426,7 +10430,7 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>CAYN JD 16/1</t>
+          <t>CAYN JD 20/1</t>
         </is>
       </c>
       <c r="H73" s="6" t="n"/>
@@ -10444,22 +10448,20 @@
         <v>1</v>
       </c>
       <c r="L73" s="10" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="M73" s="6" t="inlineStr">
-        <is>
-          <t>BLQ</t>
-        </is>
+        <v>20.54</v>
+      </c>
+      <c r="M73" s="10" t="n">
+        <v>0.05</v>
       </c>
       <c r="N73" s="10" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="O73" s="10" t="n">
-        <v>7.04</v>
+        <v>7.52</v>
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Одговара</t>
         </is>
       </c>
       <c r="Q73" s="6" t="inlineStr">
@@ -10547,33 +10549,27 @@
       <c r="A74" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="n"/>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>JD022601</t>
+          <t>JD012603_02V</t>
         </is>
       </c>
       <c r="E74" s="6" t="n"/>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>JellyDonutz</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>JD_THC20:CBD1</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>CoQ-PP-2026-0068</t>
-        </is>
-      </c>
+          <t>CAYN JD 16/1</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="n"/>
       <c r="I74" s="6" t="inlineStr">
         <is>
           <t>30.06.2026</t>
@@ -10588,18 +10584,18 @@
         <v>1</v>
       </c>
       <c r="L74" s="10" t="n">
-        <v>18.58</v>
-      </c>
-      <c r="M74" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>15.16</v>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>BLQ</t>
         </is>
       </c>
       <c r="N74" s="10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O74" s="10" t="n">
-        <v>7.73</v>
+        <v>7.04</v>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
@@ -10613,7 +10609,7 @@
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>N.D.</t>
+          <t>Одговара</t>
         </is>
       </c>
       <c r="S74" s="11" t="inlineStr">
@@ -10691,61 +10687,73 @@
       <c r="A75" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B75" s="6" t="n"/>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
       <c r="C75" s="6" t="n"/>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>P160012</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>P160012</t>
-        </is>
-      </c>
+          <t>JD022601</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n"/>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>GrapePie</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="n"/>
-      <c r="H75" s="6" t="n"/>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>JD_THC20:CBD1</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0068</t>
+        </is>
+      </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="K75" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L75" s="10" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="M75" s="10" t="n">
-        <v>0.15</v>
+        <v>18.58</v>
+      </c>
+      <c r="M75" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N75" s="10" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="O75" s="10" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="P75" s="10" t="n">
-        <v>0.42</v>
+        <v>7.73</v>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Одговара</t>
+        </is>
       </c>
       <c r="Q75" s="6" t="inlineStr">
         <is>
           <t>Одговара</t>
         </is>
       </c>
-      <c r="R75" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>Одговара</t>
         </is>
       </c>
       <c r="S75" s="11" t="inlineStr">
@@ -10827,12 +10835,12 @@
       <c r="C76" s="6" t="n"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -10856,30 +10864,28 @@
         <v>1</v>
       </c>
       <c r="L76" s="10" t="n">
-        <v>25.72</v>
+        <v>26.32</v>
       </c>
       <c r="M76" s="10" t="n">
         <v>0.15</v>
       </c>
       <c r="N76" s="10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="O76" s="10" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="P76" s="6" t="inlineStr">
+        <v>6.31</v>
+      </c>
+      <c r="P76" s="10" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
         <is>
           <t>Одговара</t>
         </is>
       </c>
-      <c r="Q76" s="6" t="inlineStr">
-        <is>
-          <t>Одговара</t>
-        </is>
-      </c>
-      <c r="R76" s="6" t="inlineStr">
-        <is>
-          <t>Одговара</t>
+      <c r="R76" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="S76" s="11" t="inlineStr">
@@ -10961,12 +10967,12 @@
       <c r="C77" s="6" t="n"/>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -10990,16 +10996,16 @@
         <v>1</v>
       </c>
       <c r="L77" s="10" t="n">
-        <v>24.78</v>
+        <v>25.72</v>
       </c>
       <c r="M77" s="10" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="N77" s="10" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="O77" s="10" t="n">
-        <v>6.78</v>
+        <v>6.67</v>
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
@@ -11091,35 +11097,25 @@
       <c r="A78" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="n">
-        <v>3</v>
-      </c>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>SCR022601</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="n"/>
+          <t>P160032</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>P160032</t>
+        </is>
+      </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>SCR_THC23:CBD1</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>CoQ-PP-2026-0069</t>
-        </is>
-      </c>
+          <t>GrapePie</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="n"/>
+      <c r="H78" s="6" t="n"/>
       <c r="I78" s="6" t="inlineStr">
         <is>
           <t>06.07.2026</t>
@@ -11134,16 +11130,16 @@
         <v>1</v>
       </c>
       <c r="L78" s="10" t="n">
-        <v>21.92</v>
+        <v>24.78</v>
       </c>
       <c r="M78" s="10" t="n">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="N78" s="10" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="O78" s="10" t="n">
-        <v>7.06</v>
+        <v>6.78</v>
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
@@ -11237,58 +11233,62 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="n"/>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>FB032601</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="E79" s="6" t="n"/>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>FB_THC11:CBD1</t>
+          <t>SCR_THC23:CBD1</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0073</t>
+          <t>CoQ-PP-2026-0069</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="K79" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L79" s="10" t="n">
-        <v>12.39</v>
+        <v>21.92</v>
       </c>
       <c r="M79" s="10" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N79" s="10" t="n">
         <v>0.06</v>
       </c>
-      <c r="N79" s="10" t="n">
-        <v>0.04</v>
-      </c>
       <c r="O79" s="10" t="n">
-        <v>7.77</v>
-      </c>
-      <c r="P79" s="10" t="n">
-        <v>0.08</v>
+        <v>7.06</v>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>Одговара</t>
+        </is>
       </c>
       <c r="Q79" s="6" t="inlineStr">
         <is>
@@ -11383,23 +11383,23 @@
       <c r="C80" s="6" t="n"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>GG032601</t>
+          <t>FB032601</t>
         </is>
       </c>
       <c r="E80" s="6" t="n"/>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>GG_THC21:CBD1</t>
+          <t>FB_THC11:CBD1</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0074</t>
+          <t>CoQ-PP-2026-0073</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
@@ -11416,21 +11416,19 @@
         <v>1</v>
       </c>
       <c r="L80" s="10" t="n">
-        <v>18.98</v>
+        <v>12.39</v>
       </c>
       <c r="M80" s="10" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="N80" s="10" t="n">
         <v>0.04</v>
       </c>
       <c r="O80" s="10" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="P80" s="6" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
+        <v>7.77</v>
+      </c>
+      <c r="P80" s="10" t="n">
+        <v>0.08</v>
       </c>
       <c r="Q80" s="6" t="inlineStr">
         <is>
@@ -11519,79 +11517,69 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="C81" s="6" t="n"/>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>P060332</t>
-        </is>
-      </c>
+          <t>GG032601</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n"/>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>CC_THC18:CBD1</t>
+          <t>GG_THC21:CBD1</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0092</t>
+          <t>CoQ-PP-2026-0074</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="K81" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L81" s="10" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="M81" s="6" t="inlineStr">
-        <is>
-          <t>&lt;LOQ</t>
-        </is>
-      </c>
-      <c r="N81" s="6" t="inlineStr">
-        <is>
-          <t>&lt;LOQ</t>
-        </is>
-      </c>
-      <c r="O81" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P81" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q81" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R81" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>18.98</v>
+      </c>
+      <c r="M81" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N81" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O81" s="10" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Одговара</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>Одговара</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>Одговара</t>
         </is>
       </c>
       <c r="S81" s="11" t="inlineStr">
@@ -11624,19 +11612,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Y81" s="6" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="Z81" s="6" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="AA81" s="6" t="inlineStr">
-        <is>
-          <t>ND</t>
+      <c r="Y81" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z81" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA81" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="AB81" s="11" t="inlineStr">
@@ -11674,32 +11662,30 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="C82" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="C82" s="6" t="n"/>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>FB012602</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>P060352</t>
+          <t>P060332</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>FB_THC16.5:CBD1</t>
+          <t>CC_THC18:CBD1</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0093</t>
+          <t>CoQ-PP-2026-0092</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
@@ -11709,17 +11695,19 @@
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="K82" s="6" t="n">
         <v>2</v>
       </c>
       <c r="L82" s="10" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="M82" s="10" t="n">
-        <v>0.22</v>
+        <v>17.67</v>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>&lt;LOQ</t>
+        </is>
       </c>
       <c r="N82" s="6" t="inlineStr">
         <is>
@@ -11776,19 +11764,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Y82" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z82" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA82" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Y82" s="6" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="Z82" s="6" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="AA82" s="6" t="inlineStr">
+        <is>
+          <t>ND</t>
         </is>
       </c>
       <c r="AB82" s="11" t="inlineStr">
@@ -11831,27 +11819,27 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>SCR012603</t>
+          <t>FB012602</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>P060382</t>
+          <t>P060352</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>SCR_THC18.5:CBD1</t>
+          <t>FB_THC16.5:CBD1</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0095</t>
+          <t>CoQ-PP-2026-0093</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -11861,111 +11849,263 @@
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="K83" s="6" t="n">
         <v>2</v>
       </c>
       <c r="L83" s="10" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="M83" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N83" s="6" t="inlineStr">
+        <is>
+          <t>&lt;LOQ</t>
+        </is>
+      </c>
+      <c r="O83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>SCR012603</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>P060382</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>SCR_THC18.5:CBD1</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0095</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L84" s="10" t="n">
         <v>17.84</v>
       </c>
-      <c r="M83" s="6" t="inlineStr">
+      <c r="M84" s="6" t="inlineStr">
         <is>
           <t>&lt;LOQ</t>
         </is>
       </c>
-      <c r="N83" s="6" t="inlineStr">
+      <c r="N84" s="6" t="inlineStr">
         <is>
           <t>&lt;LOQ</t>
         </is>
       </c>
-      <c r="O83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z83" s="6" t="inlineStr">
+      <c r="O84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z84" s="6" t="inlineStr">
         <is>
           <t>ND</t>
         </is>
       </c>
-      <c r="AA83" s="6" t="inlineStr">
+      <c r="AA84" s="6" t="inlineStr">
         <is>
           <t>ND</t>
         </is>
       </c>
-      <c r="AB83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE83" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF83" s="11" t="inlineStr">
+      <c r="AB84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE84" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF84" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11982,7 +12122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W80"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="3" max="3"/>
@@ -15228,42 +15368,42 @@
       </c>
       <c r="P29" s="20" t="inlineStr">
         <is>
+          <t>QCCoA 001v02, 04.12.2025, PP</t>
+        </is>
+      </c>
+      <c r="Q29" s="20" t="inlineStr">
+        <is>
+          <t>276-31-M-25, 04.12.2025, FHM</t>
+        </is>
+      </c>
+      <c r="R29" s="20" t="inlineStr">
+        <is>
+          <t>276-31-M-25, 04.12.2025, FHM</t>
+        </is>
+      </c>
+      <c r="S29" s="20" t="inlineStr">
+        <is>
           <t>5661-2025, 01.12.2025, IJZ</t>
         </is>
       </c>
-      <c r="Q29" s="20" t="inlineStr">
-        <is>
-          <t>276-31-M-25, 04.12.2025, FHM</t>
-        </is>
-      </c>
-      <c r="R29" s="20" t="inlineStr">
-        <is>
-          <t>276-31-M-25, 04.12.2025, FHM</t>
-        </is>
-      </c>
-      <c r="S29" s="20" t="inlineStr">
+      <c r="T29" s="20" t="inlineStr">
         <is>
           <t>5661-2025, 01.12.2025, IJZ</t>
         </is>
       </c>
-      <c r="T29" s="20" t="inlineStr">
+      <c r="U29" s="20" t="inlineStr">
         <is>
           <t>5661-2025, 01.12.2025, IJZ</t>
         </is>
       </c>
-      <c r="U29" s="20" t="inlineStr">
+      <c r="V29" s="20" t="inlineStr">
         <is>
           <t>5661-2025, 01.12.2025, IJZ</t>
         </is>
       </c>
-      <c r="V29" s="20" t="inlineStr">
-        <is>
-          <t>5661-2025, 01.12.2025, IJZ</t>
-        </is>
-      </c>
       <c r="W29" s="20" t="inlineStr">
         <is>
-          <t>5661-2025, 01.12.2025, IJZ</t>
+          <t>10802_2845-2 EN, 17.11.2025, DFL</t>
         </is>
       </c>
     </row>
@@ -18191,7 +18331,7 @@
     <row r="55">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>J31122501 (hand-trimmed)</t>
         </is>
       </c>
       <c r="B55" s="19" t="inlineStr">
@@ -18241,12 +18381,12 @@
       </c>
       <c r="K55" s="20" t="inlineStr">
         <is>
-          <t>230-0393-26, 07.04.2026, IJZ-MB</t>
+          <t>231-0394-26, 07.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="L55" s="20" t="inlineStr">
         <is>
-          <t>230-0393-26, 07.04.2026, IJZ-MB</t>
+          <t>231-0394-26, 07.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="M55" s="21" t="inlineStr">
@@ -18256,84 +18396,84 @@
       </c>
       <c r="N55" s="20" t="inlineStr">
         <is>
-          <t>230-0393-26, 07.04.2026, IJZ-MB</t>
+          <t>231-0394-26, 07.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="O55" s="20" t="inlineStr">
         <is>
-          <t>230-0393-26, 07.04.2026, IJZ-MB</t>
+          <t>231-0394-26, 07.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="P55" s="20" t="inlineStr">
         <is>
-          <t>1625-2026, 23.04.2026, IJZ</t>
+          <t>1628-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="Q55" s="20" t="inlineStr">
         <is>
-          <t>1625-2026, 23.04.2026, IJZ</t>
+          <t>1628-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="R55" s="20" t="inlineStr">
         <is>
-          <t>1625-2026, 23.04.2026, IJZ</t>
+          <t>1628-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="S55" s="20" t="inlineStr">
         <is>
-          <t>1625-2026, 23.04.2026, IJZ</t>
+          <t>1628-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="T55" s="20" t="inlineStr">
         <is>
-          <t>1625-2026, 23.04.2026, IJZ</t>
+          <t>1628-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="U55" s="20" t="inlineStr">
         <is>
-          <t>1625-2026, 23.04.2026, IJZ</t>
+          <t>1628-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="V55" s="20" t="inlineStr">
         <is>
-          <t>1625-2026, 23.04.2026, IJZ</t>
+          <t>1628-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="W55" s="20" t="inlineStr">
         <is>
-          <t>1625-2026, 23.04.2026, IJZ</t>
+          <t>1628-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>OPM122501</t>
+          <t>J31122501 (machine-trimmed)</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
-          <t>P060242</t>
+          <t>P060262</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>197-19-K-26, 07.08.2026, FHM</t>
+          <t>100-3-K-26, 09.04.2026, FHM</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>197-19-K-26, 07.08.2026, FHM</t>
+          <t>100-3-K-26, 09.04.2026, FHM</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>197-19-K-26, 07.08.2026, FHM</t>
-        </is>
-      </c>
-      <c r="F56" s="20" t="inlineStr">
-        <is>
-          <t>100-4-LoD-26, 09.04.2026, FHM</t>
+          <t>100-3-K-26, 09.04.2026, FHM</t>
+        </is>
+      </c>
+      <c r="F56" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="21" t="inlineStr">
@@ -18358,99 +18498,99 @@
       </c>
       <c r="K56" s="20" t="inlineStr">
         <is>
-          <t>229-0392-26, 07.04.2026, IJZ-MB</t>
+          <t>230-0393-26, 07.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="L56" s="20" t="inlineStr">
         <is>
-          <t>229-0392-26, 07.04.2026, IJZ-MB</t>
-        </is>
-      </c>
-      <c r="M56" s="20" t="inlineStr">
-        <is>
-          <t>229-0392-26, 07.04.2026, IJZ-MB</t>
+          <t>230-0393-26, 07.04.2026, IJZ-MB</t>
+        </is>
+      </c>
+      <c r="M56" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N56" s="20" t="inlineStr">
         <is>
-          <t>229-0392-26, 07.04.2026, IJZ-MB</t>
+          <t>230-0393-26, 07.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="O56" s="20" t="inlineStr">
         <is>
-          <t>229-0392-26, 07.04.2026, IJZ-MB</t>
+          <t>230-0393-26, 07.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="P56" s="20" t="inlineStr">
         <is>
-          <t>1627-2026, 23.04.2026, IJZ</t>
+          <t>1625-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="Q56" s="20" t="inlineStr">
         <is>
-          <t>197-19-M-26, 10.08.2026, FHM</t>
+          <t>1625-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="R56" s="20" t="inlineStr">
         <is>
-          <t>1627-2026, 23.04.2026, IJZ</t>
+          <t>1625-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="S56" s="20" t="inlineStr">
         <is>
-          <t>1627-2026, 23.04.2026, IJZ</t>
+          <t>1625-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="T56" s="20" t="inlineStr">
         <is>
-          <t>1627-2026, 23.04.2026, IJZ</t>
+          <t>1625-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="U56" s="20" t="inlineStr">
         <is>
-          <t>1627-2026, 23.04.2026, IJZ</t>
+          <t>1625-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="V56" s="20" t="inlineStr">
         <is>
-          <t>1627-2026, 23.04.2026, IJZ</t>
+          <t>1625-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="W56" s="20" t="inlineStr">
         <is>
-          <t>1627-2026, 23.04.2026, IJZ</t>
+          <t>1625-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>CC112501</t>
+          <t>OPM122501</t>
         </is>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>P060272</t>
+          <t>P060242</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>ППК26068, 11.05.2026, CNP</t>
+          <t>197-19-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
         <is>
-          <t>ППК26068, 11.05.2026, CNP</t>
+          <t>197-19-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="E57" s="20" t="inlineStr">
         <is>
-          <t>ППК26068, 11.05.2026, CNP</t>
+          <t>197-19-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="F57" s="20" t="inlineStr">
         <is>
-          <t>ППК26068, 11.05.2026, CNP</t>
+          <t>100-4-LoD-26, 09.04.2026, FHM</t>
         </is>
       </c>
       <c r="G57" s="21" t="inlineStr">
@@ -18475,99 +18615,99 @@
       </c>
       <c r="K57" s="20" t="inlineStr">
         <is>
-          <t>311-0555-26, 28.04.2026, IJZ-MB</t>
+          <t>229-0392-26, 07.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="L57" s="20" t="inlineStr">
         <is>
-          <t>311-0555-26, 28.04.2026, IJZ-MB</t>
+          <t>229-0392-26, 07.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="M57" s="20" t="inlineStr">
         <is>
-          <t>311-0555-26, 28.04.2026, IJZ-MB</t>
+          <t>229-0392-26, 07.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="N57" s="20" t="inlineStr">
         <is>
-          <t>311-0555-26, 28.04.2026, IJZ-MB</t>
+          <t>229-0392-26, 07.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="O57" s="20" t="inlineStr">
         <is>
-          <t>311-0555-26, 28.04.2026, IJZ-MB</t>
+          <t>229-0392-26, 07.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="P57" s="20" t="inlineStr">
         <is>
-          <t>2359-2026, 29.04.2026, IJZ</t>
+          <t>1627-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="Q57" s="20" t="inlineStr">
         <is>
-          <t>2359-2026, 29.04.2026, IJZ</t>
+          <t>197-19-M-26, 10.08.2026, FHM</t>
         </is>
       </c>
       <c r="R57" s="20" t="inlineStr">
         <is>
-          <t>2359-2026, 29.04.2026, IJZ</t>
+          <t>1627-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="S57" s="20" t="inlineStr">
         <is>
-          <t>2359-2026, 29.04.2026, IJZ</t>
+          <t>1627-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="T57" s="20" t="inlineStr">
         <is>
-          <t>2359-2026, 29.04.2026, IJZ</t>
+          <t>1627-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="U57" s="20" t="inlineStr">
         <is>
-          <t>2359-2026, 29.04.2026, IJZ</t>
+          <t>1627-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="V57" s="20" t="inlineStr">
         <is>
-          <t>2359-2026, 29.04.2026, IJZ</t>
+          <t>1627-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
       <c r="W57" s="20" t="inlineStr">
         <is>
-          <t>2359-2026, 29.04.2026, IJZ</t>
+          <t>1627-2026, 23.04.2026, IJZ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>FB012601_1</t>
+          <t>CC112501</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>P060322</t>
+          <t>P060272</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>ППК26067, 11.05.2026, CNP</t>
-        </is>
-      </c>
-      <c r="D58" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E58" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ППК26068, 11.05.2026, CNP</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>ППК26068, 11.05.2026, CNP</t>
+        </is>
+      </c>
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t>ППК26068, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="F58" s="20" t="inlineStr">
         <is>
-          <t>ППК26067, 11.05.2026, CNP</t>
+          <t>ППК26068, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="G58" s="21" t="inlineStr">
@@ -18592,84 +18732,84 @@
       </c>
       <c r="K58" s="20" t="inlineStr">
         <is>
-          <t>308-0552-26, 28.04.2026, IJZ-MB</t>
+          <t>311-0555-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="L58" s="20" t="inlineStr">
         <is>
-          <t>308-0552-26, 28.04.2026, IJZ-MB</t>
+          <t>311-0555-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="M58" s="20" t="inlineStr">
         <is>
-          <t>308-0552-26, 28.04.2026, IJZ-MB</t>
+          <t>311-0555-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="N58" s="20" t="inlineStr">
         <is>
-          <t>308-0552-26, 28.04.2026, IJZ-MB</t>
+          <t>311-0555-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="O58" s="20" t="inlineStr">
         <is>
-          <t>308-0552-26, 28.04.2026, IJZ-MB</t>
+          <t>311-0555-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="P58" s="20" t="inlineStr">
         <is>
-          <t>2362-2026, 30.04.2026, IJZ</t>
+          <t>2359-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="Q58" s="20" t="inlineStr">
         <is>
-          <t>2362-2026, 30.04.2026, IJZ</t>
+          <t>2359-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="R58" s="20" t="inlineStr">
         <is>
-          <t>2362-2026, 30.04.2026, IJZ</t>
+          <t>2359-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="S58" s="20" t="inlineStr">
         <is>
-          <t>2362-2026, 30.04.2026, IJZ</t>
+          <t>2359-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="T58" s="20" t="inlineStr">
         <is>
-          <t>2362-2026, 30.04.2026, IJZ</t>
+          <t>2359-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="U58" s="20" t="inlineStr">
         <is>
-          <t>2362-2026, 30.04.2026, IJZ</t>
+          <t>2359-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="V58" s="20" t="inlineStr">
         <is>
-          <t>2362-2026, 30.04.2026, IJZ</t>
+          <t>2359-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="W58" s="20" t="inlineStr">
         <is>
-          <t>2362-2026, 30.04.2026, IJZ</t>
+          <t>2359-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>FB012601_1</t>
         </is>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t>P060292</t>
+          <t>P060322</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>ППК26066, 11.05.2026, CNP</t>
+          <t>ППК26067, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="D59" s="21" t="inlineStr">
@@ -18684,7 +18824,7 @@
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
-          <t>ППК26066, 11.05.2026, CNP</t>
+          <t>ППК26067, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="G59" s="21" t="inlineStr">
@@ -18709,80 +18849,84 @@
       </c>
       <c r="K59" s="20" t="inlineStr">
         <is>
-          <t>312-0556-26, 28.04.2026, IJZ-MB</t>
+          <t>308-0552-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="L59" s="20" t="inlineStr">
         <is>
-          <t>312-0556-26, 28.04.2026, IJZ-MB</t>
+          <t>308-0552-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="M59" s="20" t="inlineStr">
         <is>
-          <t>312-0556-26, 28.04.2026, IJZ-MB</t>
+          <t>308-0552-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
-          <t>312-0556-26, 28.04.2026, IJZ-MB</t>
+          <t>308-0552-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="O59" s="20" t="inlineStr">
         <is>
-          <t>312-0556-26, 28.04.2026, IJZ-MB</t>
+          <t>308-0552-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="P59" s="20" t="inlineStr">
         <is>
-          <t>2357-2026, 29.04.2026, IJZ</t>
+          <t>2362-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="Q59" s="20" t="inlineStr">
         <is>
-          <t>2357-2026, 29.04.2026, IJZ</t>
+          <t>2362-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="R59" s="20" t="inlineStr">
         <is>
-          <t>2357-2026, 29.04.2026, IJZ</t>
+          <t>2362-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="S59" s="20" t="inlineStr">
         <is>
-          <t>2357-2026, 29.04.2026, IJZ</t>
+          <t>2362-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="T59" s="20" t="inlineStr">
         <is>
-          <t>2357-2026, 29.04.2026, IJZ</t>
+          <t>2362-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="U59" s="20" t="inlineStr">
         <is>
-          <t>2357-2026, 29.04.2026, IJZ</t>
+          <t>2362-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="V59" s="20" t="inlineStr">
         <is>
-          <t>2357-2026, 29.04.2026, IJZ</t>
+          <t>2362-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="W59" s="20" t="inlineStr">
         <is>
-          <t>2357-2026, 29.04.2026, IJZ</t>
+          <t>2362-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>GG012601*</t>
-        </is>
-      </c>
-      <c r="B60" s="19" t="n"/>
+          <t>FB112501</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>P060292</t>
+        </is>
+      </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>ППК26062, 11.05.2026, CNP</t>
+          <t>ППК26066, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="D60" s="21" t="inlineStr">
@@ -18797,7 +18941,7 @@
       </c>
       <c r="F60" s="20" t="inlineStr">
         <is>
-          <t>ППК26062, 11.05.2026, CNP</t>
+          <t>ППК26066, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="G60" s="21" t="inlineStr">
@@ -18822,89 +18966,85 @@
       </c>
       <c r="K60" s="20" t="inlineStr">
         <is>
-          <t>310-0554-26, 28.04.2026, IJZ-MB</t>
+          <t>312-0556-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="L60" s="20" t="inlineStr">
         <is>
-          <t>310-0554-26, 28.04.2026, IJZ-MB</t>
+          <t>312-0556-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="M60" s="20" t="inlineStr">
         <is>
-          <t>310-0554-26, 28.04.2026, IJZ-MB</t>
+          <t>312-0556-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="N60" s="20" t="inlineStr">
         <is>
-          <t>310-0554-26, 28.04.2026, IJZ-MB</t>
+          <t>312-0556-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="O60" s="20" t="inlineStr">
         <is>
-          <t>310-0554-26, 28.04.2026, IJZ-MB</t>
+          <t>312-0556-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="P60" s="20" t="inlineStr">
         <is>
-          <t>2364-2026, 30.04.2026, IJZ</t>
+          <t>2357-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="Q60" s="20" t="inlineStr">
         <is>
-          <t>2364-2026, 30.04.2026, IJZ</t>
+          <t>2357-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="R60" s="20" t="inlineStr">
         <is>
-          <t>2364-2026, 30.04.2026, IJZ</t>
+          <t>2357-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="S60" s="20" t="inlineStr">
         <is>
-          <t>2364-2026, 30.04.2026, IJZ</t>
+          <t>2357-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="T60" s="20" t="inlineStr">
         <is>
-          <t>2364-2026, 30.04.2026, IJZ</t>
+          <t>2357-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="U60" s="20" t="inlineStr">
         <is>
-          <t>2364-2026, 30.04.2026, IJZ</t>
+          <t>2357-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="V60" s="20" t="inlineStr">
         <is>
-          <t>2364-2026, 30.04.2026, IJZ</t>
+          <t>2357-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="W60" s="20" t="inlineStr">
         <is>
-          <t>2364-2026, 30.04.2026, IJZ</t>
+          <t>2357-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>GG112501</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>P060252</t>
-        </is>
-      </c>
+          <t>GG012601*</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="n"/>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>ППК26061, 11.05.2026, CNP</t>
-        </is>
-      </c>
-      <c r="D61" s="20" t="inlineStr">
-        <is>
-          <t>ППК26061, 11.05.2026, CNP</t>
+          <t>ППК26062, 11.05.2026, CNP</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E61" s="21" t="inlineStr">
@@ -18914,7 +19054,7 @@
       </c>
       <c r="F61" s="20" t="inlineStr">
         <is>
-          <t>ППК26061, 11.05.2026, CNP</t>
+          <t>ППК26062, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="G61" s="21" t="inlineStr">
@@ -18939,95 +19079,99 @@
       </c>
       <c r="K61" s="20" t="inlineStr">
         <is>
-          <t>304-0548-26, 28.04.2026, IJZ-MB</t>
+          <t>310-0554-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="L61" s="20" t="inlineStr">
         <is>
-          <t>304-0548-26, 28.04.2026, IJZ-MB</t>
-        </is>
-      </c>
-      <c r="M61" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>310-0554-26, 28.04.2026, IJZ-MB</t>
+        </is>
+      </c>
+      <c r="M61" s="20" t="inlineStr">
+        <is>
+          <t>310-0554-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
-          <t>304-0548-26, 28.04.2026, IJZ-MB</t>
+          <t>310-0554-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="O61" s="20" t="inlineStr">
         <is>
-          <t>304-0548-26, 28.04.2026, IJZ-MB</t>
+          <t>310-0554-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="P61" s="20" t="inlineStr">
         <is>
-          <t>2358-2026, 29.04.2026, IJZ</t>
+          <t>2364-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="Q61" s="20" t="inlineStr">
         <is>
-          <t>2358-2026, 29.04.2026, IJZ</t>
+          <t>2364-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="R61" s="20" t="inlineStr">
         <is>
-          <t>2358-2026, 29.04.2026, IJZ</t>
+          <t>2364-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="S61" s="20" t="inlineStr">
         <is>
-          <t>2358-2026, 29.04.2026, IJZ</t>
+          <t>2364-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="T61" s="20" t="inlineStr">
         <is>
-          <t>2358-2026, 29.04.2026, IJZ</t>
+          <t>2364-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="U61" s="20" t="inlineStr">
         <is>
-          <t>2358-2026, 29.04.2026, IJZ</t>
+          <t>2364-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="V61" s="20" t="inlineStr">
         <is>
-          <t>2358-2026, 29.04.2026, IJZ</t>
+          <t>2364-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="W61" s="20" t="inlineStr">
         <is>
-          <t>2358-2026, 29.04.2026, IJZ</t>
+          <t>2364-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="18" t="inlineStr">
         <is>
-          <t>JD012601*</t>
-        </is>
-      </c>
-      <c r="B62" s="19" t="n"/>
+          <t>GG112501</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>P060252</t>
+        </is>
+      </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>ППК26064, 11.05.2026, CNP</t>
+          <t>ППК26061, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>ППК26064, 11.05.2026, CNP</t>
-        </is>
-      </c>
-      <c r="E62" s="20" t="inlineStr">
-        <is>
-          <t>ППК26064, 11.05.2026, CNP</t>
+          <t>ППК26061, 11.05.2026, CNP</t>
+        </is>
+      </c>
+      <c r="E62" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
-          <t>ППК26064, 11.05.2026, CNP</t>
+          <t>ППК26061, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="G62" s="21" t="inlineStr">
@@ -19052,12 +19196,12 @@
       </c>
       <c r="K62" s="20" t="inlineStr">
         <is>
-          <t>309-0553-26, 28.04.2026, IJZ-MB</t>
+          <t>304-0548-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="L62" s="20" t="inlineStr">
         <is>
-          <t>309-0553-26, 28.04.2026, IJZ-MB</t>
+          <t>304-0548-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="M62" s="21" t="inlineStr">
@@ -19067,80 +19211,80 @@
       </c>
       <c r="N62" s="20" t="inlineStr">
         <is>
-          <t>309-0553-26, 28.04.2026, IJZ-MB</t>
+          <t>304-0548-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="O62" s="20" t="inlineStr">
         <is>
-          <t>309-0553-26, 28.04.2026, IJZ-MB</t>
+          <t>304-0548-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="P62" s="20" t="inlineStr">
         <is>
-          <t>2363-2026, 30.04.2026, IJZ</t>
+          <t>2358-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="Q62" s="20" t="inlineStr">
         <is>
-          <t>2363-2026, 30.04.2026, IJZ</t>
+          <t>2358-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="R62" s="20" t="inlineStr">
         <is>
-          <t>2363-2026, 30.04.2026, IJZ</t>
+          <t>2358-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="S62" s="20" t="inlineStr">
         <is>
-          <t>2363-2026, 30.04.2026, IJZ</t>
+          <t>2358-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="T62" s="20" t="inlineStr">
         <is>
-          <t>2363-2026, 30.04.2026, IJZ</t>
+          <t>2358-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="U62" s="20" t="inlineStr">
         <is>
-          <t>2363-2026, 30.04.2026, IJZ</t>
+          <t>2358-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="V62" s="20" t="inlineStr">
         <is>
-          <t>2363-2026, 30.04.2026, IJZ</t>
+          <t>2358-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
       <c r="W62" s="20" t="inlineStr">
         <is>
-          <t>2363-2026, 30.04.2026, IJZ</t>
+          <t>2358-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>JD112501</t>
+          <t>JD012601*</t>
         </is>
       </c>
       <c r="B63" s="19" t="n"/>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>197-15-K-26, 07.08.2026, FHM</t>
+          <t>ППК26064, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
         <is>
-          <t>197-15-K-26, 07.08.2026, FHM</t>
+          <t>ППК26064, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
-          <t>197-15-K-26, 07.08.2026, FHM</t>
+          <t>ППК26064, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="F63" s="20" t="inlineStr">
         <is>
-          <t>ППК26063, 11.05.2026, CNP</t>
+          <t>ППК26064, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="G63" s="21" t="inlineStr">
@@ -19165,12 +19309,12 @@
       </c>
       <c r="K63" s="20" t="inlineStr">
         <is>
-          <t>307-0551-26, 28.04.2026, IJZ-MB</t>
+          <t>309-0553-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="L63" s="20" t="inlineStr">
         <is>
-          <t>307-0551-26, 28.04.2026, IJZ-MB</t>
+          <t>309-0553-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="M63" s="21" t="inlineStr">
@@ -19180,80 +19324,80 @@
       </c>
       <c r="N63" s="20" t="inlineStr">
         <is>
-          <t>307-0551-26, 28.04.2026, IJZ-MB</t>
+          <t>309-0553-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="O63" s="20" t="inlineStr">
         <is>
-          <t>307-0551-26, 28.04.2026, IJZ-MB</t>
+          <t>309-0553-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="P63" s="20" t="inlineStr">
         <is>
-          <t>2361-2026, 30.04.2026, IJZ</t>
+          <t>2363-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="Q63" s="20" t="inlineStr">
         <is>
-          <t>197-15-M-26, 10.08.2026, FHM</t>
+          <t>2363-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="R63" s="20" t="inlineStr">
         <is>
-          <t>2361-2026, 30.04.2026, IJZ</t>
+          <t>2363-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="S63" s="20" t="inlineStr">
         <is>
-          <t>2361-2026, 30.04.2026, IJZ</t>
+          <t>2363-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="T63" s="20" t="inlineStr">
         <is>
-          <t>2361-2026, 30.04.2026, IJZ</t>
+          <t>2363-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="U63" s="20" t="inlineStr">
         <is>
-          <t>2361-2026, 30.04.2026, IJZ</t>
+          <t>2363-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="V63" s="20" t="inlineStr">
         <is>
-          <t>2361-2026, 30.04.2026, IJZ</t>
+          <t>2363-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="W63" s="20" t="inlineStr">
         <is>
-          <t>2361-2026, 30.04.2026, IJZ</t>
+          <t>2363-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="18" t="inlineStr">
         <is>
-          <t>JD112501*</t>
+          <t>JD112501</t>
         </is>
       </c>
       <c r="B64" s="19" t="n"/>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>ППК26065, 11.05.2026, CNP</t>
-        </is>
-      </c>
-      <c r="D64" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E64" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>197-15-K-26, 07.08.2026, FHM</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t>197-15-K-26, 07.08.2026, FHM</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t>197-15-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
-          <t>ППК26065, 11.05.2026, CNP</t>
+          <t>ППК26063, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="G64" s="21" t="inlineStr">
@@ -19278,12 +19422,12 @@
       </c>
       <c r="K64" s="20" t="inlineStr">
         <is>
-          <t>306-0550-26, 28.04.2026, IJZ-MB</t>
+          <t>307-0551-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="L64" s="20" t="inlineStr">
         <is>
-          <t>306-0550-26, 28.04.2026, IJZ-MB</t>
+          <t>307-0551-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="M64" s="21" t="inlineStr">
@@ -19293,69 +19437,65 @@
       </c>
       <c r="N64" s="20" t="inlineStr">
         <is>
-          <t>306-0550-26, 28.04.2026, IJZ-MB</t>
+          <t>307-0551-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="O64" s="20" t="inlineStr">
         <is>
-          <t>306-0550-26, 28.04.2026, IJZ-MB</t>
+          <t>307-0551-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="P64" s="20" t="inlineStr">
         <is>
-          <t>2365-2026, 30.04.2026, IJZ</t>
+          <t>2361-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="Q64" s="20" t="inlineStr">
         <is>
-          <t>2365-2026, 30.04.2026, IJZ</t>
+          <t>197-15-M-26, 10.08.2026, FHM</t>
         </is>
       </c>
       <c r="R64" s="20" t="inlineStr">
         <is>
-          <t>2365-2026, 30.04.2026, IJZ</t>
+          <t>2361-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="S64" s="20" t="inlineStr">
         <is>
-          <t>2365-2026, 30.04.2026, IJZ</t>
+          <t>2361-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="T64" s="20" t="inlineStr">
         <is>
-          <t>2365-2026, 30.04.2026, IJZ</t>
+          <t>2361-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="U64" s="20" t="inlineStr">
         <is>
-          <t>2365-2026, 30.04.2026, IJZ</t>
+          <t>2361-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="V64" s="20" t="inlineStr">
         <is>
-          <t>2365-2026, 30.04.2026, IJZ</t>
+          <t>2361-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="W64" s="20" t="inlineStr">
         <is>
-          <t>2365-2026, 30.04.2026, IJZ</t>
+          <t>2361-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>SCR112501</t>
-        </is>
-      </c>
-      <c r="B65" s="19" t="inlineStr">
-        <is>
-          <t>P060282</t>
-        </is>
-      </c>
+          <t>JD112501*</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="n"/>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>ППК26069, 11.05.2026, CNP</t>
+          <t>ППК26065, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="D65" s="21" t="inlineStr">
@@ -19370,7 +19510,7 @@
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>ППК26069, 11.05.2026, CNP</t>
+          <t>ППК26065, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="G65" s="21" t="inlineStr">
@@ -19395,12 +19535,12 @@
       </c>
       <c r="K65" s="20" t="inlineStr">
         <is>
-          <t>305-0549-26, 28.04.2026, IJZ-MB</t>
+          <t>306-0550-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="L65" s="20" t="inlineStr">
         <is>
-          <t>305-0549-26, 28.04.2026, IJZ-MB</t>
+          <t>306-0550-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="M65" s="21" t="inlineStr">
@@ -19410,95 +19550,99 @@
       </c>
       <c r="N65" s="20" t="inlineStr">
         <is>
-          <t>305-0549-26, 28.04.2026, IJZ-MB</t>
+          <t>306-0550-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="O65" s="20" t="inlineStr">
         <is>
-          <t>305-0549-26, 28.04.2026, IJZ-MB</t>
+          <t>306-0550-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="P65" s="20" t="inlineStr">
         <is>
-          <t>2360-2026, 29.04.2026, IJZ</t>
+          <t>2365-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="Q65" s="20" t="inlineStr">
         <is>
-          <t>2360-2026, 29.04.2026, IJZ</t>
+          <t>2365-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="R65" s="20" t="inlineStr">
         <is>
-          <t>2360-2026, 29.04.2026, IJZ</t>
+          <t>2365-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="S65" s="20" t="inlineStr">
         <is>
-          <t>2360-2026, 29.04.2026, IJZ</t>
+          <t>2365-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="T65" s="20" t="inlineStr">
         <is>
-          <t>2360-2026, 29.04.2026, IJZ</t>
+          <t>2365-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="U65" s="20" t="inlineStr">
         <is>
-          <t>2360-2026, 29.04.2026, IJZ</t>
+          <t>2365-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="V65" s="20" t="inlineStr">
         <is>
-          <t>2360-2026, 29.04.2026, IJZ</t>
+          <t>2365-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
       <c r="W65" s="20" t="inlineStr">
         <is>
-          <t>2360-2026, 29.04.2026, IJZ</t>
+          <t>2365-2026, 30.04.2026, IJZ</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>FB012603</t>
-        </is>
-      </c>
-      <c r="B66" s="19" t="n"/>
+          <t>SCR112501</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>P060282</t>
+        </is>
+      </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>ППК26112, 30.06.2026, CNP</t>
-        </is>
-      </c>
-      <c r="D66" s="20" t="inlineStr">
-        <is>
-          <t>ППК26112, 30.06.2026, CNP</t>
-        </is>
-      </c>
-      <c r="E66" s="20" t="inlineStr">
-        <is>
-          <t>ППК26112, 30.06.2026, CNP</t>
+          <t>ППК26069, 11.05.2026, CNP</t>
+        </is>
+      </c>
+      <c r="D66" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
-          <t>ППК26112, 30.06.2026, CNP</t>
-        </is>
-      </c>
-      <c r="G66" s="20" t="inlineStr">
-        <is>
-          <t>ППК26112, 30.06.2026, CNP</t>
-        </is>
-      </c>
-      <c r="H66" s="20" t="inlineStr">
-        <is>
-          <t>ППК26112, 30.06.2026, CNP</t>
-        </is>
-      </c>
-      <c r="I66" s="20" t="inlineStr">
-        <is>
-          <t>ППК26112, 30.06.2026, CNP</t>
+          <t>ППК26069, 11.05.2026, CNP</t>
+        </is>
+      </c>
+      <c r="G66" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J66" s="21" t="inlineStr">
@@ -19506,14 +19650,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K66" s="20" t="inlineStr">
+        <is>
+          <t>305-0549-26, 28.04.2026, IJZ-MB</t>
+        </is>
+      </c>
+      <c r="L66" s="20" t="inlineStr">
+        <is>
+          <t>305-0549-26, 28.04.2026, IJZ-MB</t>
         </is>
       </c>
       <c r="M66" s="21" t="inlineStr">
@@ -19521,101 +19665,97 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W66" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="N66" s="20" t="inlineStr">
+        <is>
+          <t>305-0549-26, 28.04.2026, IJZ-MB</t>
+        </is>
+      </c>
+      <c r="O66" s="20" t="inlineStr">
+        <is>
+          <t>305-0549-26, 28.04.2026, IJZ-MB</t>
+        </is>
+      </c>
+      <c r="P66" s="20" t="inlineStr">
+        <is>
+          <t>2360-2026, 29.04.2026, IJZ</t>
+        </is>
+      </c>
+      <c r="Q66" s="20" t="inlineStr">
+        <is>
+          <t>2360-2026, 29.04.2026, IJZ</t>
+        </is>
+      </c>
+      <c r="R66" s="20" t="inlineStr">
+        <is>
+          <t>2360-2026, 29.04.2026, IJZ</t>
+        </is>
+      </c>
+      <c r="S66" s="20" t="inlineStr">
+        <is>
+          <t>2360-2026, 29.04.2026, IJZ</t>
+        </is>
+      </c>
+      <c r="T66" s="20" t="inlineStr">
+        <is>
+          <t>2360-2026, 29.04.2026, IJZ</t>
+        </is>
+      </c>
+      <c r="U66" s="20" t="inlineStr">
+        <is>
+          <t>2360-2026, 29.04.2026, IJZ</t>
+        </is>
+      </c>
+      <c r="V66" s="20" t="inlineStr">
+        <is>
+          <t>2360-2026, 29.04.2026, IJZ</t>
+        </is>
+      </c>
+      <c r="W66" s="20" t="inlineStr">
+        <is>
+          <t>2360-2026, 29.04.2026, IJZ</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="18" t="inlineStr">
         <is>
-          <t>FB012603V</t>
-        </is>
-      </c>
-      <c r="B67" s="19" t="inlineStr">
-        <is>
-          <t>P060392</t>
-        </is>
-      </c>
+          <t>FB012603</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="n"/>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>ППК26110, 30.06.2026, CNP</t>
+          <t>ППК26112, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
         <is>
-          <t>ППК26110, 30.06.2026, CNP</t>
+          <t>ППК26112, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="E67" s="20" t="inlineStr">
         <is>
-          <t>ППК26110, 30.06.2026, CNP</t>
+          <t>ППК26112, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>ППК26110, 30.06.2026, CNP</t>
+          <t>ППК26112, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="G67" s="20" t="inlineStr">
         <is>
-          <t>ППК26110, 30.06.2026, CNP</t>
+          <t>ППК26112, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
-          <t>ППК26110, 30.06.2026, CNP</t>
+          <t>ППК26112, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>ППК26110, 30.06.2026, CNP</t>
+          <t>ППК26112, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="J67" s="21" t="inlineStr">
@@ -19692,47 +19832,47 @@
     <row r="68">
       <c r="A68" s="18" t="inlineStr">
         <is>
-          <t>GG012603</t>
+          <t>FB012603V</t>
         </is>
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>P060402</t>
+          <t>P060392</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>197-8-K-26, 07.08.2026, FHM</t>
+          <t>ППК26110, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>197-8-K-26, 07.08.2026, FHM</t>
+          <t>ППК26110, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>197-8-K-26, 07.08.2026, FHM</t>
+          <t>ППК26110, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
-          <t>ППК26114, 30.06.2026, CNP</t>
+          <t>ППК26110, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="G68" s="20" t="inlineStr">
         <is>
-          <t>ППК26114, 30.06.2026, CNP</t>
+          <t>ППК26110, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="H68" s="20" t="inlineStr">
         <is>
-          <t>ППК26114, 30.06.2026, CNP</t>
+          <t>ППК26110, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
-          <t>ППК26114, 30.06.2026, CNP</t>
+          <t>ППК26110, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="J68" s="21" t="inlineStr">
@@ -19765,19 +19905,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P68" s="20" t="inlineStr">
-        <is>
-          <t>197-8-M-26, 10.08.2026, FHM</t>
-        </is>
-      </c>
-      <c r="Q68" s="20" t="inlineStr">
-        <is>
-          <t>197-8-M-26, 10.08.2026, FHM</t>
-        </is>
-      </c>
-      <c r="R68" s="20" t="inlineStr">
-        <is>
-          <t>197-8-M-26, 10.08.2026, FHM</t>
+      <c r="P68" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q68" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R68" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="S68" s="21" t="inlineStr">
@@ -19809,43 +19949,47 @@
     <row r="69">
       <c r="A69" s="18" t="inlineStr">
         <is>
-          <t>JD012603_02</t>
-        </is>
-      </c>
-      <c r="B69" s="19" t="n"/>
+          <t>GG012603</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>P060402</t>
+        </is>
+      </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>ППК26113, 30.06.2026, CNP</t>
+          <t>197-8-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>ППК26113, 30.06.2026, CNP</t>
+          <t>197-8-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>ППК26113, 30.06.2026, CNP</t>
+          <t>197-8-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>ППК26113, 30.06.2026, CNP</t>
+          <t>ППК26114, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="G69" s="20" t="inlineStr">
         <is>
-          <t>ППК26113, 30.06.2026, CNP</t>
+          <t>ППК26114, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="H69" s="20" t="inlineStr">
         <is>
-          <t>ППК26113, 30.06.2026, CNP</t>
+          <t>ППК26114, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="I69" s="20" t="inlineStr">
         <is>
-          <t>ППК26113, 30.06.2026, CNP</t>
+          <t>ППК26114, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="J69" s="21" t="inlineStr">
@@ -19878,19 +20022,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P69" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q69" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R69" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="P69" s="20" t="inlineStr">
+        <is>
+          <t>197-8-M-26, 10.08.2026, FHM</t>
+        </is>
+      </c>
+      <c r="Q69" s="20" t="inlineStr">
+        <is>
+          <t>197-8-M-26, 10.08.2026, FHM</t>
+        </is>
+      </c>
+      <c r="R69" s="20" t="inlineStr">
+        <is>
+          <t>197-8-M-26, 10.08.2026, FHM</t>
         </is>
       </c>
       <c r="S69" s="21" t="inlineStr">
@@ -19922,43 +20066,43 @@
     <row r="70">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>JD012603_02V</t>
+          <t>JD012603_02</t>
         </is>
       </c>
       <c r="B70" s="19" t="n"/>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>ППК26111, 30.06.2026, CNP</t>
+          <t>ППК26113, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>ППК26111, 30.06.2026, CNP</t>
+          <t>ППК26113, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>ППК26111, 30.06.2026, CNP</t>
+          <t>ППК26113, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="F70" s="20" t="inlineStr">
         <is>
-          <t>ППК26111, 30.06.2026, CNP</t>
+          <t>ППК26113, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="G70" s="20" t="inlineStr">
         <is>
-          <t>ППК26111, 30.06.2026, CNP</t>
+          <t>ППК26113, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="H70" s="20" t="inlineStr">
         <is>
-          <t>ППК26111, 30.06.2026, CNP</t>
+          <t>ППК26113, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
-          <t>ППК26111, 30.06.2026, CNP</t>
+          <t>ППК26113, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="J70" s="21" t="inlineStr">
@@ -20035,43 +20179,43 @@
     <row r="71">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>JD022601</t>
+          <t>JD012603_02V</t>
         </is>
       </c>
       <c r="B71" s="19" t="n"/>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>ППК26115, 30.06.2026, CNP</t>
-        </is>
-      </c>
-      <c r="D71" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ППК26111, 30.06.2026, CNP</t>
+        </is>
+      </c>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <t>ППК26111, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>ППК26115, 30.06.2026, CNP</t>
+          <t>ППК26111, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>ППК26115, 30.06.2026, CNP</t>
+          <t>ППК26111, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="G71" s="20" t="inlineStr">
         <is>
-          <t>ППК26115, 30.06.2026, CNP</t>
+          <t>ППК26111, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="H71" s="20" t="inlineStr">
         <is>
-          <t>ППК26115, 30.06.2026, CNP</t>
+          <t>ППК26111, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>ППК26115, 30.06.2026, CNP</t>
+          <t>ППК26111, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="J71" s="21" t="inlineStr">
@@ -20148,47 +20292,43 @@
     <row r="72">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>P160012</t>
-        </is>
-      </c>
-      <c r="B72" s="19" t="inlineStr">
-        <is>
-          <t>P160012</t>
-        </is>
-      </c>
+          <t>JD022601</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="n"/>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>ППК26117, 06.07.2026, CNP</t>
-        </is>
-      </c>
-      <c r="D72" s="20" t="inlineStr">
-        <is>
-          <t>ППК26117, 06.07.2026, CNP</t>
+          <t>ППК26115, 30.06.2026, CNP</t>
+        </is>
+      </c>
+      <c r="D72" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>ППК26117, 06.07.2026, CNP</t>
+          <t>ППК26115, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
         <is>
-          <t>ППК26117, 06.07.2026, CNP</t>
+          <t>ППК26115, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="G72" s="20" t="inlineStr">
         <is>
-          <t>ППК26117, 06.07.2026, CNP</t>
+          <t>ППК26115, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="H72" s="20" t="inlineStr">
         <is>
-          <t>ППК26117, 06.07.2026, CNP</t>
-        </is>
-      </c>
-      <c r="I72" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ППК26115, 30.06.2026, CNP</t>
+        </is>
+      </c>
+      <c r="I72" s="20" t="inlineStr">
+        <is>
+          <t>ППК26115, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="J72" s="21" t="inlineStr">
@@ -20265,47 +20405,47 @@
     <row r="73">
       <c r="A73" s="18" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>ППК26118, 06.07.2026, CNP</t>
+          <t>ППК26117, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>ППК26118, 06.07.2026, CNP</t>
+          <t>ППК26117, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>ППК26118, 06.07.2026, CNP</t>
+          <t>ППК26117, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>ППК26118, 06.07.2026, CNP</t>
+          <t>ППК26117, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="G73" s="20" t="inlineStr">
         <is>
-          <t>ППК26118, 06.07.2026, CNP</t>
+          <t>ППК26117, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
-          <t>ППК26118, 06.07.2026, CNP</t>
-        </is>
-      </c>
-      <c r="I73" s="20" t="inlineStr">
-        <is>
-          <t>ППК26118, 06.07.2026, CNP</t>
+          <t>ППК26117, 06.07.2026, CNP</t>
+        </is>
+      </c>
+      <c r="I73" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J73" s="21" t="inlineStr">
@@ -20382,47 +20522,47 @@
     <row r="74">
       <c r="A74" s="18" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="B74" s="19" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>ППК26119, 06.07.2026, CNP</t>
+          <t>ППК26118, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>ППК26119, 06.07.2026, CNP</t>
+          <t>ППК26118, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>ППК26119, 06.07.2026, CNP</t>
+          <t>ППК26118, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>ППК26119, 06.07.2026, CNP</t>
+          <t>ППК26118, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="G74" s="20" t="inlineStr">
         <is>
-          <t>ППК26119, 06.07.2026, CNP</t>
+          <t>ППК26118, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="H74" s="20" t="inlineStr">
         <is>
-          <t>ППК26119, 06.07.2026, CNP</t>
+          <t>ППК26118, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
-          <t>ППК26119, 06.07.2026, CNP</t>
+          <t>ППК26118, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="J74" s="21" t="inlineStr">
@@ -20499,43 +20639,47 @@
     <row r="75">
       <c r="A75" s="18" t="inlineStr">
         <is>
-          <t>SCR022601</t>
-        </is>
-      </c>
-      <c r="B75" s="19" t="n"/>
+          <t>P160032</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>P160032</t>
+        </is>
+      </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>ППК26116, 06.07.2026, CNP</t>
+          <t>ППК26119, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>ППК26116, 06.07.2026, CNP</t>
+          <t>ППК26119, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>ППК26116, 06.07.2026, CNP</t>
+          <t>ППК26119, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>ППК26116, 06.07.2026, CNP</t>
+          <t>ППК26119, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="G75" s="20" t="inlineStr">
         <is>
-          <t>ППК26116, 06.07.2026, CNP</t>
+          <t>ППК26119, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="H75" s="20" t="inlineStr">
         <is>
-          <t>ППК26116, 06.07.2026, CNP</t>
+          <t>ППК26119, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>ППК26116, 06.07.2026, CNP</t>
+          <t>ППК26119, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="J75" s="21" t="inlineStr">
@@ -20612,43 +20756,43 @@
     <row r="76">
       <c r="A76" s="18" t="inlineStr">
         <is>
-          <t>FB032601</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="B76" s="19" t="n"/>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>ППК26127, 21.07.2026, CNP</t>
+          <t>ППК26116, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>ППК26127, 21.07.2026, CNP</t>
+          <t>ППК26116, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>ППК26127, 21.07.2026, CNP</t>
+          <t>ППК26116, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
         <is>
-          <t>ППК26127, 21.07.2026, CNP</t>
+          <t>ППК26116, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="G76" s="20" t="inlineStr">
         <is>
-          <t>ППК26127, 21.07.2026, CNP</t>
+          <t>ППК26116, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="H76" s="20" t="inlineStr">
         <is>
-          <t>ППК26127, 21.07.2026, CNP</t>
+          <t>ППК26116, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
-          <t>ППК26127, 21.07.2026, CNP</t>
+          <t>ППК26116, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="J76" s="21" t="inlineStr">
@@ -20725,43 +20869,43 @@
     <row r="77">
       <c r="A77" s="18" t="inlineStr">
         <is>
-          <t>GG032601</t>
+          <t>FB032601</t>
         </is>
       </c>
       <c r="B77" s="19" t="n"/>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>ППК26128, 21.07.2026, CNP</t>
+          <t>ППК26127, 21.07.2026, CNP</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
         <is>
-          <t>ППК26128, 21.07.2026, CNP</t>
+          <t>ППК26127, 21.07.2026, CNP</t>
         </is>
       </c>
       <c r="E77" s="20" t="inlineStr">
         <is>
-          <t>ППК26128, 21.07.2026, CNP</t>
+          <t>ППК26127, 21.07.2026, CNP</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>ППК26128, 21.07.2026, CNP</t>
+          <t>ППК26127, 21.07.2026, CNP</t>
         </is>
       </c>
       <c r="G77" s="20" t="inlineStr">
         <is>
-          <t>ППК26128, 21.07.2026, CNP</t>
+          <t>ППК26127, 21.07.2026, CNP</t>
         </is>
       </c>
       <c r="H77" s="20" t="inlineStr">
         <is>
-          <t>ППК26128, 21.07.2026, CNP</t>
+          <t>ППК26127, 21.07.2026, CNP</t>
         </is>
       </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>ППК26128, 21.07.2026, CNP</t>
+          <t>ППК26127, 21.07.2026, CNP</t>
         </is>
       </c>
       <c r="J77" s="21" t="inlineStr">
@@ -20838,47 +20982,43 @@
     <row r="78">
       <c r="A78" s="18" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
-        </is>
-      </c>
-      <c r="B78" s="19" t="inlineStr">
-        <is>
-          <t>P060332</t>
-        </is>
-      </c>
+          <t>GG032601</t>
+        </is>
+      </c>
+      <c r="B78" s="19" t="n"/>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>197-6-K-26, 07.08.2026, FHM</t>
+          <t>ППК26128, 21.07.2026, CNP</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>197-6-K-26, 07.08.2026, FHM</t>
+          <t>ППК26128, 21.07.2026, CNP</t>
         </is>
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>197-6-K-26, 07.08.2026, FHM</t>
-        </is>
-      </c>
-      <c r="F78" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ППК26128, 21.07.2026, CNP</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>ППК26128, 21.07.2026, CNP</t>
+        </is>
+      </c>
+      <c r="G78" s="20" t="inlineStr">
+        <is>
+          <t>ППК26128, 21.07.2026, CNP</t>
+        </is>
+      </c>
+      <c r="H78" s="20" t="inlineStr">
+        <is>
+          <t>ППК26128, 21.07.2026, CNP</t>
+        </is>
+      </c>
+      <c r="I78" s="20" t="inlineStr">
+        <is>
+          <t>ППК26128, 21.07.2026, CNP</t>
         </is>
       </c>
       <c r="J78" s="21" t="inlineStr">
@@ -20911,19 +21051,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P78" s="20" t="inlineStr">
-        <is>
-          <t>197-6-M-26, 10.08.2026, FHM</t>
-        </is>
-      </c>
-      <c r="Q78" s="20" t="inlineStr">
-        <is>
-          <t>197-6-M-26, 10.08.2026, FHM</t>
-        </is>
-      </c>
-      <c r="R78" s="20" t="inlineStr">
-        <is>
-          <t>197-6-M-26, 10.08.2026, FHM</t>
+      <c r="P78" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q78" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R78" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="S78" s="21" t="inlineStr">
@@ -20955,27 +21095,27 @@
     <row r="79">
       <c r="A79" s="18" t="inlineStr">
         <is>
-          <t>FB012602</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="B79" s="19" t="inlineStr">
         <is>
-          <t>P060352</t>
+          <t>P060332</t>
         </is>
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>197-7-K-26, 07.08.2026, FHM</t>
+          <t>197-6-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
         <is>
-          <t>197-7-K-26, 07.08.2026, FHM</t>
+          <t>197-6-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="E79" s="20" t="inlineStr">
         <is>
-          <t>197-7-K-26, 07.08.2026, FHM</t>
+          <t>197-6-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="F79" s="21" t="inlineStr">
@@ -21028,19 +21168,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P79" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q79" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R79" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="P79" s="20" t="inlineStr">
+        <is>
+          <t>197-6-M-26, 10.08.2026, FHM</t>
+        </is>
+      </c>
+      <c r="Q79" s="20" t="inlineStr">
+        <is>
+          <t>197-6-M-26, 10.08.2026, FHM</t>
+        </is>
+      </c>
+      <c r="R79" s="20" t="inlineStr">
+        <is>
+          <t>197-6-M-26, 10.08.2026, FHM</t>
         </is>
       </c>
       <c r="S79" s="21" t="inlineStr">
@@ -21072,115 +21212,232 @@
     <row r="80">
       <c r="A80" s="18" t="inlineStr">
         <is>
+          <t>FB012602</t>
+        </is>
+      </c>
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>P060352</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>197-7-K-26, 07.08.2026, FHM</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>197-7-K-26, 07.08.2026, FHM</t>
+        </is>
+      </c>
+      <c r="E80" s="20" t="inlineStr">
+        <is>
+          <t>197-7-K-26, 07.08.2026, FHM</t>
+        </is>
+      </c>
+      <c r="F80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W80" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
           <t>SCR012603</t>
         </is>
       </c>
-      <c r="B80" s="19" t="inlineStr">
+      <c r="B81" s="19" t="inlineStr">
         <is>
           <t>P060382</t>
         </is>
       </c>
-      <c r="C80" s="20" t="inlineStr">
+      <c r="C81" s="20" t="inlineStr">
         <is>
           <t>197-21-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
-      <c r="D80" s="20" t="inlineStr">
+      <c r="D81" s="20" t="inlineStr">
         <is>
           <t>197-21-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
-      <c r="E80" s="20" t="inlineStr">
+      <c r="E81" s="20" t="inlineStr">
         <is>
           <t>197-21-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
-      <c r="F80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q80" s="20" t="inlineStr">
+      <c r="F81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q81" s="20" t="inlineStr">
         <is>
           <t>197-21-M-26, 10.08.2026, FHM</t>
         </is>
       </c>
-      <c r="R80" s="20" t="inlineStr">
+      <c r="R81" s="20" t="inlineStr">
         <is>
           <t>197-21-M-26, 10.08.2026, FHM</t>
         </is>
       </c>
-      <c r="S80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V80" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W80" s="21" t="inlineStr">
+      <c r="S81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V81" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W81" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -22040,38 +22297,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId850"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId851"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R56" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T56" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U56" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V56" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W56" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R57" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T57" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U57" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V57" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W57" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R56" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T56" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U56" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V56" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W56" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R57" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T57" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U57" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V57" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W57" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId884"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId885"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId886"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId887"/>
@@ -22117,10 +22374,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V60" r:id="rId927"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W60" r:id="rId928"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId933"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId934"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId935"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId936"/>
@@ -22133,163 +22390,178 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W61" r:id="rId943"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId944"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R62" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S62" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T62" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U62" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V62" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W62" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R63" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S63" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T63" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U63" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V63" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W63" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R64" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T64" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U64" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V64" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W64" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R65" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T65" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U65" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V65" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W65" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId1024"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId1025"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q68" r:id="rId1026"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R68" r:id="rId1027"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId1028"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId1029"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId1030"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId1031"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId1032"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId1041"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId1042"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId1043"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId1044"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId1045"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId1046"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId1047"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId1048"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId1049"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId1050"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId1051"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId1052"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId1053"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId1054"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId1055"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId1056"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId1057"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId1058"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId1059"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId1060"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId1061"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId1062"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId1063"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId1064"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId1065"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId1066"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId1067"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId1068"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId1069"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId1070"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId1071"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId1072"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId1073"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId1074"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId1075"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId1076"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId1077"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId1078"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId1079"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId1080"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId1081"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId1082"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId1083"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId1084"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId1085"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId1086"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId1087"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId1088"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId1089"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId1090"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId1091"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId1092"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q78" r:id="rId1093"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R78" r:id="rId1094"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId1095"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId1096"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId1097"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId1098"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId1099"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId1100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId1101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R80" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R62" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S62" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T62" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U62" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V62" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W62" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R63" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S63" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T63" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U63" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V63" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W63" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R64" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T64" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U64" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V64" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W64" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R65" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T65" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U65" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V65" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W65" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R66" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S66" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T66" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U66" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V66" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W66" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q69" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R69" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q79" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R79" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R81" r:id="rId1117"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22301,7 +22573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -22733,8 +23005,8 @@
       <c r="F13" s="22" t="inlineStr">
         <is>
           <t>QCCoA 001 · 10.07.2025 · PP
+472-0863-25 · 22.05.2025 · IJZ-MB
 ППК25140 · 22.05.2025 · CNP
-472-0863-25 · 22.05.2025 · IJZ-MB
 2472-2025 · 30.05.2025 · IJZ</t>
         </is>
       </c>
@@ -22772,8 +23044,8 @@
         <is>
           <t>627-1128-25 · 02.07.2025 · IJZ-MB
 197-11-K-26 · 07.08.2026 · FHM
+ППК25174 · 10.07.2025 · CNP
 QCCoA 001 · 10.07.2025 · PP
-ППК25174 · 10.07.2025 · CNP
 197-11-M-26 · 10.08.2026 · FHM
 QCCoA 001 · 17.07.2025 · PP
 3176-2025 · 26.06.2025 · IJZ</t>
@@ -23013,8 +23285,8 @@
       <c r="F20" s="22" t="inlineStr">
         <is>
           <t>QCCoA 001v02 · 21.01.2026 · PP
+ППК25210 · 28.07.2025 · CNP
 3636-2025 · 28.07.2025 · IJZ
-ППК25210 · 28.07.2025 · CNP
 766-1375-25 · 29.07.2025 · IJZ-MB</t>
         </is>
       </c>
@@ -23086,8 +23358,8 @@
         <is>
           <t>197-3-K-26 · 07.08.2026 · FHM
 4350-2025 · 15.09.2025 · IJZ
+949-1687-25 · 17.09.2025 · IJZ-MB
 ППК25280 · 17.09.2025 · CNP
-949-1687-25 · 17.09.2025 · IJZ-MB
 QCCoA 001 · 22.09.2025 · PP</t>
         </is>
       </c>
@@ -23358,6 +23630,7 @@
           <t>5661-2025 · 01.12.2025 · IJZ
 276-31-M-25 · 04.12.2025 · FHM
 QCCoA 001v02 · 04.12.2025 · PP
+10802_2845-2 EN · 17.11.2025 · DFL
 1157-2058-25 · 24.11.2025 · IJZ-MB</t>
         </is>
       </c>
@@ -23544,8 +23817,8 @@
       <c r="F34" s="22" t="inlineStr">
         <is>
           <t>1228-2194-25 · 05.12.2025 · IJZ-MB
+ППК25378 · 12.12.2025 · CNP
 5886-2025 · 12.12.2025 · IJZ
-ППК25378 · 12.12.2025 · CNP
 QCCoA 001v02 · 21.01.2026 · PP</t>
         </is>
       </c>
@@ -23582,8 +23855,8 @@
       <c r="F35" s="22" t="inlineStr">
         <is>
           <t>1229-2195-25 · 05.12.2025 · IJZ-MB
+5887-2025 · 12.12.2025 · IJZ
 ППК25379 · 12.12.2025 · CNP
-5887-2025 · 12.12.2025 · IJZ
 QCCoA 001v02 · 21.01.2026 · PP</t>
         </is>
       </c>
@@ -23660,8 +23933,8 @@
           <t>1227-2193-25 · 05.12.2025 · IJZ-MB
 197-12-K-26 · 07.08.2026 · FHM
 197-12-M-26 · 10.08.2026 · FHM
+ППК25381 · 12.12.2025 · CNP
 5889-2025 · 12.12.2025 · IJZ
-ППК25381 · 12.12.2025 · CNP
 QCCoA 001v02 · 21.01.2026 · PP</t>
         </is>
       </c>
@@ -24107,8 +24380,8 @@
       </c>
       <c r="F49" s="22" t="inlineStr">
         <is>
-          <t>100-1-LoD-26 · 09.04.2026 · FHM
-100-1-K-26 · 09.04.2026 · FHM</t>
+          <t>100-1-K-26 · 09.04.2026 · FHM
+100-1-LoD-26 · 09.04.2026 · FHM</t>
         </is>
       </c>
       <c r="G49" s="22" t="inlineStr">
@@ -24299,14 +24572,10 @@
       <c r="A55" s="22" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="22" t="inlineStr">
-        <is>
-          <t>CoQ-PP-2026-0054</t>
-        </is>
-      </c>
+      <c r="B55" s="22" t="n"/>
       <c r="C55" s="22" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>J31122501 (hand-trimmed)</t>
         </is>
       </c>
       <c r="D55" s="22" t="inlineStr">
@@ -24321,9 +24590,9 @@
       </c>
       <c r="F55" s="22" t="inlineStr">
         <is>
-          <t>230-0393-26 · 07.04.2026 · IJZ-MB
+          <t>231-0394-26 · 07.04.2026 · IJZ-MB
 100-2-K-26 · 09.04.2026 · FHM
-1625-2026 · 23.04.2026 · IJZ</t>
+1628-2026 · 23.04.2026 · IJZ</t>
         </is>
       </c>
       <c r="G55" s="22" t="inlineStr">
@@ -24338,25 +24607,62 @@
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
+          <t>CoQ-PP-2026-0054</t>
+        </is>
+      </c>
+      <c r="C56" s="22" t="inlineStr">
+        <is>
+          <t>J31122501 (machine-trimmed)</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="inlineStr">
+        <is>
+          <t>P060262</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
+        <is>
+          <t>230-0393-26 · 07.04.2026 · IJZ-MB
+100-3-K-26 · 09.04.2026 · FHM
+1625-2026 · 23.04.2026 · IJZ</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
           <t>CoQ-PP-2026-0055</t>
         </is>
       </c>
-      <c r="C56" s="22" t="inlineStr">
+      <c r="C57" s="22" t="inlineStr">
         <is>
           <t>OPM122501</t>
         </is>
       </c>
-      <c r="D56" s="22" t="inlineStr">
+      <c r="D57" s="22" t="inlineStr">
         <is>
           <t>P060242</t>
         </is>
       </c>
-      <c r="E56" s="22" t="inlineStr">
+      <c r="E57" s="22" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="F56" s="22" t="inlineStr">
+      <c r="F57" s="22" t="inlineStr">
         <is>
           <t>229-0392-26 · 07.04.2026 · IJZ-MB
 197-19-K-26 · 07.08.2026 · FHM
@@ -24365,7 +24671,7 @@
 1627-2026 · 23.04.2026 · IJZ</t>
         </is>
       </c>
-      <c r="G56" s="22" t="inlineStr">
+      <c r="G57" s="22" t="inlineStr">
         <is>
           <t>Total Δ9-THC: 8.09 (100-4-K-26, 09.04.2026, FHM) → 7.91 (197-19-K-26, 07.08.2026, FHM), +120d
 Total CBD: &lt;LOQ (100-4-K-26, 09.04.2026, FHM) → &lt;LOQ (197-19-K-26, 07.08.2026, FHM), +120d
@@ -24374,221 +24680,221 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="22" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="22" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="22" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
         <is>
           <t>CoQ-PP-2026-0056</t>
         </is>
       </c>
-      <c r="C57" s="22" t="inlineStr">
+      <c r="C58" s="22" t="inlineStr">
         <is>
           <t>CC112501</t>
         </is>
       </c>
-      <c r="D57" s="22" t="inlineStr">
+      <c r="D58" s="22" t="inlineStr">
         <is>
           <t>P060272</t>
         </is>
       </c>
-      <c r="E57" s="22" t="inlineStr">
+      <c r="E58" s="22" t="inlineStr">
         <is>
           <t>Cash Cow</t>
         </is>
       </c>
-      <c r="F57" s="22" t="inlineStr">
+      <c r="F58" s="22" t="inlineStr">
         <is>
           <t>ППК26068 · 11.05.2026 · CNP
 311-0555-26 · 28.04.2026 · IJZ-MB
 2359-2026 · 29.04.2026 · IJZ</t>
         </is>
       </c>
-      <c r="G57" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="22" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" s="22" t="inlineStr">
+      <c r="G58" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
         <is>
           <t>CoQ-PP-2026-0061</t>
         </is>
       </c>
-      <c r="C58" s="22" t="inlineStr">
+      <c r="C59" s="22" t="inlineStr">
         <is>
           <t>FB012601_1</t>
         </is>
       </c>
-      <c r="D58" s="22" t="inlineStr">
+      <c r="D59" s="22" t="inlineStr">
         <is>
           <t>P060322</t>
         </is>
       </c>
-      <c r="E58" s="22" t="inlineStr">
+      <c r="E59" s="22" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
       </c>
-      <c r="F58" s="22" t="inlineStr">
+      <c r="F59" s="22" t="inlineStr">
         <is>
           <t>ППК26067 · 11.05.2026 · CNP
 308-0552-26 · 28.04.2026 · IJZ-MB
 2362-2026 · 30.04.2026 · IJZ</t>
         </is>
       </c>
-      <c r="G58" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="22" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="22" t="inlineStr">
+      <c r="G59" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
         <is>
           <t>CoQ-PP-2026-0057</t>
         </is>
       </c>
-      <c r="C59" s="22" t="inlineStr">
+      <c r="C60" s="22" t="inlineStr">
         <is>
           <t>FB112501</t>
         </is>
       </c>
-      <c r="D59" s="22" t="inlineStr">
+      <c r="D60" s="22" t="inlineStr">
         <is>
           <t>P060292</t>
         </is>
       </c>
-      <c r="E59" s="22" t="inlineStr">
+      <c r="E60" s="22" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
       </c>
-      <c r="F59" s="22" t="inlineStr">
+      <c r="F60" s="22" t="inlineStr">
         <is>
           <t>ППК26066 · 11.05.2026 · CNP
 312-0556-26 · 28.04.2026 · IJZ-MB
 2357-2026 · 29.04.2026 · IJZ</t>
         </is>
       </c>
-      <c r="G59" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="22" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" s="22" t="n"/>
-      <c r="C60" s="22" t="inlineStr">
+      <c r="G60" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="22" t="n"/>
+      <c r="C61" s="22" t="inlineStr">
         <is>
           <t>GG012601*</t>
         </is>
       </c>
-      <c r="D60" s="22" t="n"/>
-      <c r="E60" s="22" t="n"/>
-      <c r="F60" s="22" t="inlineStr">
+      <c r="D61" s="22" t="n"/>
+      <c r="E61" s="22" t="n"/>
+      <c r="F61" s="22" t="inlineStr">
         <is>
           <t>ППК26062 · 11.05.2026 · CNP
 310-0554-26 · 28.04.2026 · IJZ-MB
 2364-2026 · 30.04.2026 · IJZ</t>
         </is>
       </c>
-      <c r="G60" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="22" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" s="22" t="inlineStr">
+      <c r="G61" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
         <is>
           <t>CoQ-PP-2026-0058</t>
         </is>
       </c>
-      <c r="C61" s="22" t="inlineStr">
+      <c r="C62" s="22" t="inlineStr">
         <is>
           <t>GG112501</t>
         </is>
       </c>
-      <c r="D61" s="22" t="inlineStr">
+      <c r="D62" s="22" t="inlineStr">
         <is>
           <t>P060252</t>
         </is>
       </c>
-      <c r="E61" s="22" t="inlineStr">
+      <c r="E62" s="22" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
       </c>
-      <c r="F61" s="22" t="inlineStr">
+      <c r="F62" s="22" t="inlineStr">
         <is>
           <t>ППК26061 · 11.05.2026 · CNP
 304-0548-26 · 28.04.2026 · IJZ-MB
 2358-2026 · 29.04.2026 · IJZ</t>
         </is>
       </c>
-      <c r="G61" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="22" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="22" t="n"/>
-      <c r="C62" s="22" t="inlineStr">
+      <c r="G62" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="22" t="n"/>
+      <c r="C63" s="22" t="inlineStr">
         <is>
           <t>JD012601*</t>
         </is>
       </c>
-      <c r="D62" s="22" t="n"/>
-      <c r="E62" s="22" t="n"/>
-      <c r="F62" s="22" t="inlineStr">
+      <c r="D63" s="22" t="n"/>
+      <c r="E63" s="22" t="n"/>
+      <c r="F63" s="22" t="inlineStr">
         <is>
           <t>ППК26064 · 11.05.2026 · CNP
 309-0553-26 · 28.04.2026 · IJZ-MB
 2363-2026 · 30.04.2026 · IJZ</t>
         </is>
       </c>
-      <c r="G62" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="22" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="22" t="n"/>
-      <c r="C63" s="22" t="inlineStr">
+      <c r="G63" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="22" t="n"/>
+      <c r="C64" s="22" t="inlineStr">
         <is>
           <t>JD112501</t>
         </is>
       </c>
-      <c r="D63" s="22" t="n"/>
-      <c r="E63" s="22" t="inlineStr">
+      <c r="D64" s="22" t="n"/>
+      <c r="E64" s="22" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
       </c>
-      <c r="F63" s="22" t="inlineStr">
+      <c r="F64" s="22" t="inlineStr">
         <is>
           <t>197-15-K-26 · 07.08.2026 · FHM
 197-15-M-26 · 10.08.2026 · FHM
@@ -24597,100 +24903,69 @@
 2361-2026 · 30.04.2026 · IJZ</t>
         </is>
       </c>
-      <c r="G63" s="22" t="inlineStr">
+      <c r="G64" s="22" t="inlineStr">
         <is>
           <t>Total Δ9-THC: 19.64 (ППК26063, 11.05.2026, CNP) → 20.32 (197-15-K-26, 07.08.2026, FHM), +88d
 Aflatoxin B1: Н.Д. (2361-2026, 30.04.2026, IJZ) → ND (197-15-M-26, 10.08.2026, FHM), +102d</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="22" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="22" t="n"/>
-      <c r="C64" s="22" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="22" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="22" t="n"/>
+      <c r="C65" s="22" t="inlineStr">
         <is>
           <t>JD112501*</t>
         </is>
       </c>
-      <c r="D64" s="22" t="n"/>
-      <c r="E64" s="22" t="n"/>
-      <c r="F64" s="22" t="inlineStr">
+      <c r="D65" s="22" t="n"/>
+      <c r="E65" s="22" t="n"/>
+      <c r="F65" s="22" t="inlineStr">
         <is>
           <t>ППК26065 · 11.05.2026 · CNP
 306-0550-26 · 28.04.2026 · IJZ-MB
 2365-2026 · 30.04.2026 · IJZ</t>
         </is>
       </c>
-      <c r="G64" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="22" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" s="22" t="inlineStr">
+      <c r="G65" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
         <is>
           <t>CoQ-PP-2026-0060</t>
         </is>
       </c>
-      <c r="C65" s="22" t="inlineStr">
+      <c r="C66" s="22" t="inlineStr">
         <is>
           <t>SCR112501</t>
         </is>
       </c>
-      <c r="D65" s="22" t="inlineStr">
+      <c r="D66" s="22" t="inlineStr">
         <is>
           <t>P060282</t>
         </is>
       </c>
-      <c r="E65" s="22" t="inlineStr">
+      <c r="E66" s="22" t="inlineStr">
         <is>
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="F65" s="22" t="inlineStr">
+      <c r="F66" s="22" t="inlineStr">
         <is>
           <t>ППК26069 · 11.05.2026 · CNP
 305-0549-26 · 28.04.2026 · IJZ-MB
 2360-2026 · 29.04.2026 · IJZ</t>
         </is>
       </c>
-      <c r="G65" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="22" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" s="22" t="inlineStr">
-        <is>
-          <t>CoQ-PP-2026-0064</t>
-        </is>
-      </c>
-      <c r="C66" s="22" t="inlineStr">
-        <is>
-          <t>FB012603</t>
-        </is>
-      </c>
-      <c r="D66" s="22" t="n"/>
-      <c r="E66" s="22" t="inlineStr">
-        <is>
-          <t>Fat Bastard</t>
-        </is>
-      </c>
-      <c r="F66" s="22" t="inlineStr">
-        <is>
-          <t>ППК26112 · 30.06.2026 · CNP</t>
-        </is>
-      </c>
       <c r="G66" s="22" t="inlineStr">
         <is>
           <t>—</t>
@@ -24703,19 +24978,15 @@
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0065</t>
+          <t>CoQ-PP-2026-0064</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>FB012603V</t>
-        </is>
-      </c>
-      <c r="D67" s="22" t="inlineStr">
-        <is>
-          <t>P060392</t>
-        </is>
-      </c>
+          <t>FB012603</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="n"/>
       <c r="E67" s="22" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
@@ -24723,7 +24994,7 @@
       </c>
       <c r="F67" s="22" t="inlineStr">
         <is>
-          <t>ППК26110 · 30.06.2026 · CNP</t>
+          <t>ППК26112 · 30.06.2026 · CNP</t>
         </is>
       </c>
       <c r="G67" s="22" t="inlineStr">
@@ -24738,58 +25009,66 @@
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
+          <t>CoQ-PP-2026-0065</t>
+        </is>
+      </c>
+      <c r="C68" s="22" t="inlineStr">
+        <is>
+          <t>FB012603V</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="inlineStr">
+        <is>
+          <t>P060392</t>
+        </is>
+      </c>
+      <c r="E68" s="22" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="F68" s="22" t="inlineStr">
+        <is>
+          <t>ППК26110 · 30.06.2026 · CNP</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
           <t>CoQ-PP-2026-0094</t>
         </is>
       </c>
-      <c r="C68" s="22" t="inlineStr">
+      <c r="C69" s="22" t="inlineStr">
         <is>
           <t>GG012603</t>
         </is>
       </c>
-      <c r="D68" s="22" t="inlineStr">
+      <c r="D69" s="22" t="inlineStr">
         <is>
           <t>P060402</t>
         </is>
       </c>
-      <c r="E68" s="22" t="inlineStr">
+      <c r="E69" s="22" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
       </c>
-      <c r="F68" s="22" t="inlineStr">
+      <c r="F69" s="22" t="inlineStr">
         <is>
           <t>197-8-K-26 · 07.08.2026 · FHM
 197-8-M-26 · 10.08.2026 · FHM
 ППК26114 · 30.06.2026 · CNP</t>
         </is>
       </c>
-      <c r="G68" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="22" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" s="22" t="n"/>
-      <c r="C69" s="22" t="inlineStr">
-        <is>
-          <t>JD012603_02</t>
-        </is>
-      </c>
-      <c r="D69" s="22" t="n"/>
-      <c r="E69" s="22" t="inlineStr">
-        <is>
-          <t>JellyDonutz</t>
-        </is>
-      </c>
-      <c r="F69" s="22" t="inlineStr">
-        <is>
-          <t>ППК26113 · 30.06.2026 · CNP</t>
-        </is>
-      </c>
       <c r="G69" s="22" t="inlineStr">
         <is>
           <t>—</t>
@@ -24803,7 +25082,7 @@
       <c r="B70" s="22" t="n"/>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>JD012603_02V</t>
+          <t>JD012603_02</t>
         </is>
       </c>
       <c r="D70" s="22" t="n"/>
@@ -24814,7 +25093,7 @@
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t>ППК26111 · 30.06.2026 · CNP</t>
+          <t>ППК26113 · 30.06.2026 · CNP</t>
         </is>
       </c>
       <c r="G70" s="22" t="inlineStr">
@@ -24827,25 +25106,21 @@
       <c r="A71" s="22" t="n">
         <v>69</v>
       </c>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>CoQ-PP-2026-0068</t>
-        </is>
-      </c>
+      <c r="B71" s="22" t="n"/>
       <c r="C71" s="22" t="inlineStr">
         <is>
-          <t>JD022601</t>
+          <t>JD012603_02V</t>
         </is>
       </c>
       <c r="D71" s="22" t="n"/>
       <c r="E71" s="22" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>JellyDonutz</t>
         </is>
       </c>
       <c r="F71" s="22" t="inlineStr">
         <is>
-          <t>ППК26115 · 30.06.2026 · CNP</t>
+          <t>ППК26111 · 30.06.2026 · CNP</t>
         </is>
       </c>
       <c r="G71" s="22" t="inlineStr">
@@ -24858,25 +25133,25 @@
       <c r="A72" s="22" t="n">
         <v>70</v>
       </c>
-      <c r="B72" s="22" t="n"/>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0068</t>
+        </is>
+      </c>
       <c r="C72" s="22" t="inlineStr">
         <is>
-          <t>P160012</t>
-        </is>
-      </c>
-      <c r="D72" s="22" t="inlineStr">
-        <is>
-          <t>P160012</t>
-        </is>
-      </c>
+          <t>JD022601</t>
+        </is>
+      </c>
+      <c r="D72" s="22" t="n"/>
       <c r="E72" s="22" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t>ППК26117 · 06.07.2026 · CNP</t>
+          <t>ППК26115 · 30.06.2026 · CNP</t>
         </is>
       </c>
       <c r="G72" s="22" t="inlineStr">
@@ -24892,12 +25167,12 @@
       <c r="B73" s="22" t="n"/>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="E73" s="22" t="inlineStr">
@@ -24907,7 +25182,7 @@
       </c>
       <c r="F73" s="22" t="inlineStr">
         <is>
-          <t>ППК26118 · 06.07.2026 · CNP</t>
+          <t>ППК26117 · 06.07.2026 · CNP</t>
         </is>
       </c>
       <c r="G73" s="22" t="inlineStr">
@@ -24923,12 +25198,12 @@
       <c r="B74" s="22" t="n"/>
       <c r="C74" s="22" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="E74" s="22" t="inlineStr">
@@ -24938,7 +25213,7 @@
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t>ППК26119 · 06.07.2026 · CNP</t>
+          <t>ППК26118 · 06.07.2026 · CNP</t>
         </is>
       </c>
       <c r="G74" s="22" t="inlineStr">
@@ -24951,25 +25226,25 @@
       <c r="A75" s="22" t="n">
         <v>73</v>
       </c>
-      <c r="B75" s="22" t="inlineStr">
-        <is>
-          <t>CoQ-PP-2026-0069</t>
-        </is>
-      </c>
+      <c r="B75" s="22" t="n"/>
       <c r="C75" s="22" t="inlineStr">
         <is>
-          <t>SCR022601</t>
-        </is>
-      </c>
-      <c r="D75" s="22" t="n"/>
+          <t>P160032</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="inlineStr">
+        <is>
+          <t>P160032</t>
+        </is>
+      </c>
       <c r="E75" s="22" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>GrapePie</t>
         </is>
       </c>
       <c r="F75" s="22" t="inlineStr">
         <is>
-          <t>ППК26116 · 06.07.2026 · CNP</t>
+          <t>ППК26119 · 06.07.2026 · CNP</t>
         </is>
       </c>
       <c r="G75" s="22" t="inlineStr">
@@ -24984,23 +25259,23 @@
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0073</t>
+          <t>CoQ-PP-2026-0069</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>FB032601</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="D76" s="22" t="n"/>
       <c r="E76" s="22" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t>ППК26127 · 21.07.2026 · CNP</t>
+          <t>ППК26116 · 06.07.2026 · CNP</t>
         </is>
       </c>
       <c r="G76" s="22" t="inlineStr">
@@ -25015,23 +25290,23 @@
       </c>
       <c r="B77" s="22" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0074</t>
+          <t>CoQ-PP-2026-0073</t>
         </is>
       </c>
       <c r="C77" s="22" t="inlineStr">
         <is>
-          <t>GG032601</t>
+          <t>FB032601</t>
         </is>
       </c>
       <c r="D77" s="22" t="n"/>
       <c r="E77" s="22" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="F77" s="22" t="inlineStr">
         <is>
-          <t>ППК26128 · 21.07.2026 · CNP</t>
+          <t>ППК26127 · 21.07.2026 · CNP</t>
         </is>
       </c>
       <c r="G77" s="22" t="inlineStr">
@@ -25046,28 +25321,23 @@
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0092</t>
+          <t>CoQ-PP-2026-0074</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
-        </is>
-      </c>
-      <c r="D78" s="22" t="inlineStr">
-        <is>
-          <t>P060332</t>
-        </is>
-      </c>
+          <t>GG032601</t>
+        </is>
+      </c>
+      <c r="D78" s="22" t="n"/>
       <c r="E78" s="22" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t>197-6-K-26 · 07.08.2026 · FHM
-197-6-M-26 · 10.08.2026 · FHM</t>
+          <t>ППК26128 · 21.07.2026 · CNP</t>
         </is>
       </c>
       <c r="G78" s="22" t="inlineStr">
@@ -25082,27 +25352,28 @@
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0093</t>
+          <t>CoQ-PP-2026-0092</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>FB012602</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>P060352</t>
+          <t>P060332</t>
         </is>
       </c>
       <c r="E79" s="22" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="F79" s="22" t="inlineStr">
         <is>
-          <t>197-7-K-26 · 07.08.2026 · FHM</t>
+          <t>197-6-K-26 · 07.08.2026 · FHM
+197-6-M-26 · 10.08.2026 · FHM</t>
         </is>
       </c>
       <c r="G79" s="22" t="inlineStr">
@@ -25117,31 +25388,66 @@
       </c>
       <c r="B80" s="22" t="inlineStr">
         <is>
+          <t>CoQ-PP-2026-0093</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="inlineStr">
+        <is>
+          <t>FB012602</t>
+        </is>
+      </c>
+      <c r="D80" s="22" t="inlineStr">
+        <is>
+          <t>P060352</t>
+        </is>
+      </c>
+      <c r="E80" s="22" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="F80" s="22" t="inlineStr">
+        <is>
+          <t>197-7-K-26 · 07.08.2026 · FHM</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
           <t>CoQ-PP-2026-0095</t>
         </is>
       </c>
-      <c r="C80" s="22" t="inlineStr">
+      <c r="C81" s="22" t="inlineStr">
         <is>
           <t>SCR012603</t>
         </is>
       </c>
-      <c r="D80" s="22" t="inlineStr">
+      <c r="D81" s="22" t="inlineStr">
         <is>
           <t>P060382</t>
         </is>
       </c>
-      <c r="E80" s="22" t="inlineStr">
+      <c r="E81" s="22" t="inlineStr">
         <is>
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="F80" s="22" t="inlineStr">
+      <c r="F81" s="22" t="inlineStr">
         <is>
           <t>197-21-K-26 · 07.08.2026 · FHM
 197-21-M-26 · 10.08.2026 · FHM</t>
         </is>
       </c>
-      <c r="G80" s="22" t="inlineStr">
+      <c r="G81" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -26274,7 +26580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -26982,26 +27288,40 @@
     <row r="43">
       <c r="A43" s="31" t="inlineStr">
         <is>
-          <t>FB012601_1</t>
+          <t>J31122501 (hand-trimmed)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="31" t="inlineStr">
         <is>
-          <t>GG012601*</t>
+          <t>J31122501 (machine-trimmed)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="31" t="inlineStr">
         <is>
-          <t>JD012601*</t>
+          <t>FB012601_1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>GG012601*</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>JD012601*</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="31" t="inlineStr">
         <is>
           <t>JD112501*</t>
         </is>

--- a/deliverables/qc_register/PP_Batch_QC_Testing_Results_Register.xlsx
+++ b/deliverables/qc_register/PP_Batch_QC_Testing_Results_Register.xlsx
@@ -9582,7 +9582,11 @@
           <t>JD112501</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n"/>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
@@ -10422,7 +10426,11 @@
           <t>JD012603_02</t>
         </is>
       </c>
-      <c r="E73" s="6" t="n"/>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>P060412</t>
+        </is>
+      </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
           <t>JellyDonutz</t>
@@ -10558,7 +10566,11 @@
           <t>JD012603_02V</t>
         </is>
       </c>
-      <c r="E74" s="6" t="n"/>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>P060422</t>
+        </is>
+      </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
           <t>JellyDonutz</t>
@@ -19379,7 +19391,11 @@
           <t>JD112501</t>
         </is>
       </c>
-      <c r="B64" s="19" t="n"/>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
           <t>197-15-K-26, 07.08.2026, FHM</t>
@@ -20069,7 +20085,11 @@
           <t>JD012603_02</t>
         </is>
       </c>
-      <c r="B70" s="19" t="n"/>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>P060412</t>
+        </is>
+      </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
           <t>ППК26113, 30.06.2026, CNP</t>
@@ -20182,7 +20202,11 @@
           <t>JD012603_02V</t>
         </is>
       </c>
-      <c r="B71" s="19" t="n"/>
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>P060422</t>
+        </is>
+      </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
           <t>ППК26111, 30.06.2026, CNP</t>
@@ -23005,8 +23029,8 @@
       <c r="F13" s="22" t="inlineStr">
         <is>
           <t>QCCoA 001 · 10.07.2025 · PP
+ППК25140 · 22.05.2025 · CNP
 472-0863-25 · 22.05.2025 · IJZ-MB
-ППК25140 · 22.05.2025 · CNP
 2472-2025 · 30.05.2025 · IJZ</t>
         </is>
       </c>
@@ -23044,8 +23068,8 @@
         <is>
           <t>627-1128-25 · 02.07.2025 · IJZ-MB
 197-11-K-26 · 07.08.2026 · FHM
+QCCoA 001 · 10.07.2025 · PP
 ППК25174 · 10.07.2025 · CNP
-QCCoA 001 · 10.07.2025 · PP
 197-11-M-26 · 10.08.2026 · FHM
 QCCoA 001 · 17.07.2025 · PP
 3176-2025 · 26.06.2025 · IJZ</t>
@@ -23393,8 +23417,8 @@
       <c r="F23" s="22" t="inlineStr">
         <is>
           <t>4349-2025 · 15.09.2025 · IJZ
+ППК25281 · 17.09.2025 · CNP
 947-1685-25 · 17.09.2025 · IJZ-MB
-ППК25281 · 17.09.2025 · CNP
 QCCoA 001v02 · 21.01.2026 · PP</t>
         </is>
       </c>
@@ -23628,8 +23652,8 @@
       <c r="F29" s="22" t="inlineStr">
         <is>
           <t>5661-2025 · 01.12.2025 · IJZ
+QCCoA 001v02 · 04.12.2025 · PP
 276-31-M-25 · 04.12.2025 · FHM
-QCCoA 001v02 · 04.12.2025 · PP
 10802_2845-2 EN · 17.11.2025 · DFL
 1157-2058-25 · 24.11.2025 · IJZ-MB</t>
         </is>
@@ -23817,8 +23841,8 @@
       <c r="F34" s="22" t="inlineStr">
         <is>
           <t>1228-2194-25 · 05.12.2025 · IJZ-MB
+5886-2025 · 12.12.2025 · IJZ
 ППК25378 · 12.12.2025 · CNP
-5886-2025 · 12.12.2025 · IJZ
 QCCoA 001v02 · 21.01.2026 · PP</t>
         </is>
       </c>
@@ -23933,8 +23957,8 @@
           <t>1227-2193-25 · 05.12.2025 · IJZ-MB
 197-12-K-26 · 07.08.2026 · FHM
 197-12-M-26 · 10.08.2026 · FHM
+5889-2025 · 12.12.2025 · IJZ
 ППК25381 · 12.12.2025 · CNP
-5889-2025 · 12.12.2025 · IJZ
 QCCoA 001v02 · 21.01.2026 · PP</t>
         </is>
       </c>
@@ -24888,7 +24912,11 @@
           <t>JD112501</t>
         </is>
       </c>
-      <c r="D64" s="22" t="n"/>
+      <c r="D64" s="22" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
       <c r="E64" s="22" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
@@ -25085,7 +25113,11 @@
           <t>JD012603_02</t>
         </is>
       </c>
-      <c r="D70" s="22" t="n"/>
+      <c r="D70" s="22" t="inlineStr">
+        <is>
+          <t>P060412</t>
+        </is>
+      </c>
       <c r="E70" s="22" t="inlineStr">
         <is>
           <t>JellyDonutz</t>
@@ -25112,7 +25144,11 @@
           <t>JD012603_02V</t>
         </is>
       </c>
-      <c r="D71" s="22" t="n"/>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>P060422</t>
+        </is>
+      </c>
       <c r="E71" s="22" t="inlineStr">
         <is>
           <t>JellyDonutz</t>

--- a/deliverables/qc_register/PP_Batch_QC_Testing_Results_Register.xlsx
+++ b/deliverables/qc_register/PP_Batch_QC_Testing_Results_Register.xlsx
@@ -9196,8 +9196,16 @@
           <t>GG012601*</t>
         </is>
       </c>
-      <c r="E64" s="6" t="n"/>
-      <c r="F64" s="6" t="n"/>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>P060302</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
       <c r="G64" s="6" t="n"/>
       <c r="H64" s="6" t="n"/>
       <c r="I64" s="6" t="inlineStr">
@@ -9460,8 +9468,16 @@
           <t>JD012601*</t>
         </is>
       </c>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>P060312</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
       <c r="G66" s="6" t="n"/>
       <c r="H66" s="6" t="n"/>
       <c r="I66" s="6" t="inlineStr">
@@ -9717,7 +9733,11 @@
         </is>
       </c>
       <c r="E68" s="6" t="n"/>
-      <c r="F68" s="6" t="n"/>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
       <c r="G68" s="6" t="n"/>
       <c r="H68" s="6" t="n"/>
       <c r="I68" s="6" t="inlineStr">
@@ -19048,7 +19068,11 @@
           <t>GG012601*</t>
         </is>
       </c>
-      <c r="B61" s="19" t="n"/>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>P060302</t>
+        </is>
+      </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
           <t>ППК26062, 11.05.2026, CNP</t>
@@ -19278,7 +19302,11 @@
           <t>JD012601*</t>
         </is>
       </c>
-      <c r="B63" s="19" t="n"/>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>P060312</t>
+        </is>
+      </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
           <t>ППК26064, 11.05.2026, CNP</t>
@@ -23068,8 +23096,8 @@
         <is>
           <t>627-1128-25 · 02.07.2025 · IJZ-MB
 197-11-K-26 · 07.08.2026 · FHM
+ППК25174 · 10.07.2025 · CNP
 QCCoA 001 · 10.07.2025 · PP
-ППК25174 · 10.07.2025 · CNP
 197-11-M-26 · 10.08.2026 · FHM
 QCCoA 001 · 17.07.2025 · PP
 3176-2025 · 26.06.2025 · IJZ</t>
@@ -23309,8 +23337,8 @@
       <c r="F20" s="22" t="inlineStr">
         <is>
           <t>QCCoA 001v02 · 21.01.2026 · PP
+3636-2025 · 28.07.2025 · IJZ
 ППК25210 · 28.07.2025 · CNP
-3636-2025 · 28.07.2025 · IJZ
 766-1375-25 · 29.07.2025 · IJZ-MB</t>
         </is>
       </c>
@@ -23417,8 +23445,8 @@
       <c r="F23" s="22" t="inlineStr">
         <is>
           <t>4349-2025 · 15.09.2025 · IJZ
+947-1685-25 · 17.09.2025 · IJZ-MB
 ППК25281 · 17.09.2025 · CNP
-947-1685-25 · 17.09.2025 · IJZ-MB
 QCCoA 001v02 · 21.01.2026 · PP</t>
         </is>
       </c>
@@ -23652,8 +23680,8 @@
       <c r="F29" s="22" t="inlineStr">
         <is>
           <t>5661-2025 · 01.12.2025 · IJZ
+276-31-M-25 · 04.12.2025 · FHM
 QCCoA 001v02 · 04.12.2025 · PP
-276-31-M-25 · 04.12.2025 · FHM
 10802_2845-2 EN · 17.11.2025 · DFL
 1157-2058-25 · 24.11.2025 · IJZ-MB</t>
         </is>
@@ -23841,8 +23869,8 @@
       <c r="F34" s="22" t="inlineStr">
         <is>
           <t>1228-2194-25 · 05.12.2025 · IJZ-MB
+ППК25378 · 12.12.2025 · CNP
 5886-2025 · 12.12.2025 · IJZ
-ППК25378 · 12.12.2025 · CNP
 QCCoA 001v02 · 21.01.2026 · PP</t>
         </is>
       </c>
@@ -23917,8 +23945,8 @@
       <c r="F36" s="22" t="inlineStr">
         <is>
           <t>1226-2192-25 · 05.12.2025 · IJZ-MB
+5888-2025 · 12.12.2025 · IJZ
 ППК25380 · 12.12.2025 · CNP
-5888-2025 · 12.12.2025 · IJZ
 QCCoA 001v02 · 21.01.2026 · PP</t>
         </is>
       </c>
@@ -23957,8 +23985,8 @@
           <t>1227-2193-25 · 05.12.2025 · IJZ-MB
 197-12-K-26 · 07.08.2026 · FHM
 197-12-M-26 · 10.08.2026 · FHM
+ППК25381 · 12.12.2025 · CNP
 5889-2025 · 12.12.2025 · IJZ
-ППК25381 · 12.12.2025 · CNP
 QCCoA 001v02 · 21.01.2026 · PP</t>
         </is>
       </c>
@@ -24404,8 +24432,8 @@
       </c>
       <c r="F49" s="22" t="inlineStr">
         <is>
-          <t>100-1-K-26 · 09.04.2026 · FHM
-100-1-LoD-26 · 09.04.2026 · FHM</t>
+          <t>100-1-LoD-26 · 09.04.2026 · FHM
+100-1-K-26 · 09.04.2026 · FHM</t>
         </is>
       </c>
       <c r="G49" s="22" t="inlineStr">
@@ -24825,8 +24853,16 @@
           <t>GG012601*</t>
         </is>
       </c>
-      <c r="D61" s="22" t="n"/>
-      <c r="E61" s="22" t="n"/>
+      <c r="D61" s="22" t="inlineStr">
+        <is>
+          <t>P060302</t>
+        </is>
+      </c>
+      <c r="E61" s="22" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
       <c r="F61" s="22" t="inlineStr">
         <is>
           <t>ППК26062 · 11.05.2026 · CNP
@@ -24887,8 +24923,16 @@
           <t>JD012601*</t>
         </is>
       </c>
-      <c r="D63" s="22" t="n"/>
-      <c r="E63" s="22" t="n"/>
+      <c r="D63" s="22" t="inlineStr">
+        <is>
+          <t>P060312</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
       <c r="F63" s="22" t="inlineStr">
         <is>
           <t>ППК26064 · 11.05.2026 · CNP
@@ -24949,7 +24993,11 @@
         </is>
       </c>
       <c r="D65" s="22" t="n"/>
-      <c r="E65" s="22" t="n"/>
+      <c r="E65" s="22" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
       <c r="F65" s="22" t="inlineStr">
         <is>
           <t>ППК26065 · 11.05.2026 · CNP
